--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33307.957</t>
+          <t>32130.24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,42 +1024,42 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-1135.33</t>
+          <t>-591.64</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-97.83</t>
+          <t>-104.53</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1499279569.454414</t>
+          <t>1499161354.892341</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>892390121.6</t>
+          <t>956584872.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>905448004.3</t>
+          <t>919270819.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1847387257.46</t>
+          <t>1860013080.08</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-13057882</t>
+          <t>37314052</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-204554850.1885323</t>
+          <t>-208720390.647228</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-252793170.36</v>
+        <v>-231630863.17</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,72 +1177,72 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.3711118857815312</t>
+          <t>-11.1876022432316</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-30.08244799405779</t>
+          <t>-27.53874609309782</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-16.80652098253021</t>
+          <t>-17.9987389236193</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>131774</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35754.726</t>
+          <t>33307.957</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,37 +1460,37 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-283.59</t>
+          <t>-1135.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>-97.83</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1499279569.454414</t>
+          <t>1499161354.892341</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>850962782.6</t>
+          <t>892390121.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>944921985.7</t>
+          <t>905448004.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1839319197.86</t>
+          <t>1847387257.46</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-93959203</t>
+          <t>-13057882</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-195784246.5206898</t>
+          <t>-204554850.1885323</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-279963404.27</v>
+        <v>-252793170.36</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,72 +1608,72 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.3711118857815312</t>
+          <t>-11.1876022432316</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-30.08244799405779</t>
+          <t>-27.53874609309782</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-16.80652098253021</t>
+          <t>-17.9987389236193</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>131774</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,32 +1688,32 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19100.069</t>
+          <t>35754.726</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-25.70</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,17 +1871,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-169.18</t>
+          <t>-283.59</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-85.75</t>
+          <t>-91.66</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1499279569.454414</t>
+          <t>1499161354.892341</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>588369533.0</t>
+          <t>1108572562.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>753461962.0</t>
+          <t>850962782.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1014121978.2</t>
+          <t>944921985.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1826207989.06</t>
+          <t>1839319197.86</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-260660016</t>
+          <t>-93959203</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-180478945.112572</t>
+          <t>-195784246.5206898</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-320340047.87</v>
+        <v>-279963404.27</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,72 +2039,72 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.3711118857815312</t>
+          <t>-11.1876022432316</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-30.08244799405779</t>
+          <t>-27.53874609309782</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-16.80652098253021</t>
+          <t>-17.9987389236193</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>131774</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,32 +2119,32 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>36914.823</t>
+          <t>19100.069</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-35.38</t>
+          <t>-25.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-118.78</t>
+          <t>-169.18</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-85.75</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1499279569.454414</t>
+          <t>1499161354.892341</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1140326331.0</t>
+          <t>588369533.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>828070288.4</t>
+          <t>753461962.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1281460447.9</t>
+          <t>1014121978.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1821954460.44</t>
+          <t>1826207989.06</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-453390159</t>
+          <t>-260660016</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-155049653.7024488</t>
+          <t>-180478945.112572</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-310844212.48</v>
+        <v>-320340047.87</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,72 +2470,72 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.3711118857815312</t>
+          <t>-11.1876022432316</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-30.08244799405779</t>
+          <t>-27.53874609309782</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-16.80652098253021</t>
+          <t>-17.9987389236193</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>131774</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,32 +2550,32 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19843.161</t>
+          <t>36914.823</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-35.38</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-118.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-73.71</t>
+          <t>-79.73</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1499279569.454414</t>
+          <t>1499161354.892341</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>624009643.0</t>
+          <t>1140326331.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>881956766.8</t>
+          <t>828070288.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1357437409.7</t>
+          <t>1281460447.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1805702267.22</t>
+          <t>1821954460.44</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-475480642</t>
+          <t>-453390159</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-126723370.2875744</t>
+          <t>-155049653.7024488</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-345315382.7</v>
+        <v>-310844212.48</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,72 +2901,72 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.3711118857815312</t>
+          <t>-11.1876022432316</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-30.08244799405779</t>
+          <t>-27.53874609309782</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-16.80652098253021</t>
+          <t>-17.9987389236193</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>131774</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24826.953</t>
+          <t>19843.161</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-8.61</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-42.95</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-63.68</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-68.39</t>
+          <t>-73.71</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1499279569.454414</t>
+          <t>1499161354.892341</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>793535844.0</t>
+          <t>624009643.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>918505887.0</t>
+          <t>881956766.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1610063469.2</t>
+          <t>1357437409.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1809298292.6</t>
+          <t>1805702267.22</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-691557582</t>
+          <t>-475480642</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-86979368.03002107</t>
+          <t>-126723370.2875744</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-326907574.21</v>
+        <v>-345315382.7</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.3711118857815312</t>
+          <t>-11.1876022432316</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-30.08244799405779</t>
+          <t>-27.53874609309782</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-16.80652098253021</t>
+          <t>-17.9987389236193</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,42 +3362,42 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>131774</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,32 +3412,32 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19032.948</t>
+          <t>24826.953</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.7</t>
+          <t>-8.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-43.01</t>
+          <t>-42.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,260 +3615,260 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>32.37</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>33.14</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>31.32</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>30.46</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-63.68</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-68.39</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>1499161354.892341</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>793535844.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>918505887.0</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>1610063469.2</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>1809298292.6</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-691557582</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-86979368.03002107</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>-326907574.21</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2025/09/24</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-8.26</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>-11.1876022432316</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-27.53874609309782</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-17.9987389236193</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>4.82</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>42.95</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>19.24</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>5.67%</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>23.47</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>128028</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>C電子產品99.60%、其他0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>仁寶-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>32.5</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
           <t>32.65</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.15</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>30.42</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-48.04</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-63.36</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>1499279569.454414</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>621068459.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1038881188.8</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>1822971879.1</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1803713391.36</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-784090690</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-43356057.81596284</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-307098955.95</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>2025/09/24</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-5.80</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.3711118857815312</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-30.08244799405779</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-16.80652098253021</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>4.68</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>41.41</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>19.8</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>5.87%</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>1.45%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>23.67</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>131774</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>C電子產品99.60%、其他0.40% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>仁寶-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業平上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>30149.028</t>
+          <t>19032.948</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-48.45</t>
+          <t>-43.01</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>31.24</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>30.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-41.67</t>
+          <t>-48.04</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-58.96</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1499279569.454414</t>
+          <t>1499161354.892341</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>961411165.0</t>
+          <t>621068459.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>1274781994.4</t>
+          <t>1038881188.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2473123750.7</t>
+          <t>1822971879.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1798901888.5</t>
+          <t>1803713391.36</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1198341756</t>
+          <t>-784090690</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4597196.391051546</t>
+          <t>-43356057.81596284</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-249354461.63</v>
+        <v>-307098955.95</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,27 +4194,27 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.3711118857815312</t>
+          <t>-11.1876022432316</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-30.08244799405779</t>
+          <t>-27.53874609309782</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-16.80652098253021</t>
+          <t>-17.9987389236193</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,42 +4224,42 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>131774</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,32 +4274,32 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43281.83</t>
+          <t>30149.028</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.19</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-38.16</t>
+          <t>-48.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,32 +4472,32 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>32.92</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4507,27 +4507,27 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-41.67</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-54.68</t>
+          <t>-58.96</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1499279569.454414</t>
+          <t>1499161354.892341</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1409758723.0</t>
+          <t>961411165.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1734850607.4</t>
+          <t>1274781994.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2805199811.8</t>
+          <t>2473123750.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1785814116.68</t>
+          <t>1798901888.5</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1070349204</t>
+          <t>-1198341756</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>50770225.12228593</t>
+          <t>4597196.391051546</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-194422100.32</v>
+        <v>-249354461.63</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,72 +4625,72 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.3711118857815312</t>
+          <t>-11.1876022432316</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-30.08244799405779</t>
+          <t>-27.53874609309782</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-16.80652098253021</t>
+          <t>-17.9987389236193</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>131774</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,32 +4705,32 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24186.087</t>
+          <t>43281.83</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-11.2</t>
+          <t>-11.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-35.57</t>
+          <t>-38.16</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>33.16</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-29.49</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-51.34</t>
+          <t>-54.68</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1499279569.454414</t>
+          <t>1499161354.892341</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>806755244.0</t>
+          <t>1409758723.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1832918052.6</t>
+          <t>1734850607.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2844796368.0</t>
+          <t>2805199811.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1768788111.4</t>
+          <t>1785814116.68</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1011878315</t>
+          <t>-1070349204</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>95350647.93073882</t>
+          <t>50770225.12228593</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-157040890.37</v>
+        <v>-194422100.32</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.3711118857815312</t>
+          <t>-11.1876022432316</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-30.08244799405779</t>
+          <t>-27.53874609309782</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-16.80652098253021</t>
+          <t>-17.9987389236193</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,42 +5086,42 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>131774</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5151,17 +5151,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42004.369</t>
+          <t>24186.087</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,72 +5203,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>33.25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-14.46</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-5.78</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-35.57</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>33.05</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-10.54</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-4.83</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-26.89</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.17</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,195 +5319,195 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>348</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>33.84</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.17</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>30.29</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-9.56</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-51.34</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>1499161354.892341</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>806755244.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>1832918052.6</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>2844796368.0</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>1768788111.4</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-1011878315</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>95350647.93073882</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>-157040890.37</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>2025/09/24</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>-3.62</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-49.28</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>1499279569.454414</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>1395412353.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>2301621051.4</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>3148082913.2</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1761224974.54</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-846461861</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>141240018.5317318</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-33423043.04</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>2025/09/24</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.3711118857815312</t>
+          <t>-11.1876022432316</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-30.08244799405779</t>
+          <t>-27.53874609309782</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-16.80652098253021</t>
+          <t>-17.9987389236193</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,42 +5517,42 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.24</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>5.87%</t>
+          <t>5.67%</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>23.67</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>131774</t>
+          <t>128028</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,17 +5567,17 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>29.17</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32130.24</t>
+          <t>43018.944</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-591.64</t>
+          <t>-242.93</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.53</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1499161354.892341</t>
+          <t>1499662850.984848</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>956584872.0</t>
+          <t>974746025.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>919270819.4</t>
+          <t>901408156.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1860013080.08</t>
+          <t>1876762391.38</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>37314052</t>
+          <t>73337868</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-208720390.647228</t>
+          <t>-205773457.290989</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-231630863.17</v>
+        <v>-189565323.83</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33307.957</t>
+          <t>32130.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,42 +1455,42 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1135.33</t>
+          <t>-591.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-97.83</t>
+          <t>-104.53</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1499161354.892341</t>
+          <t>1499662850.984848</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>892390121.6</t>
+          <t>956584872.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>905448004.3</t>
+          <t>919270819.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1847387257.46</t>
+          <t>1860013080.08</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-13057882</t>
+          <t>37314052</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-204554850.1885323</t>
+          <t>-208720390.647228</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-252793170.36</v>
+        <v>-231630863.17</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35754.726</t>
+          <t>33307.957</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,37 +1891,37 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-283.59</t>
+          <t>-1135.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>-97.83</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1499161354.892341</t>
+          <t>1499662850.984848</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>850962782.6</t>
+          <t>892390121.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>944921985.7</t>
+          <t>905448004.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1839319197.86</t>
+          <t>1847387257.46</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-93959203</t>
+          <t>-13057882</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-195784246.5206898</t>
+          <t>-204554850.1885323</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-279963404.27</v>
+        <v>-252793170.36</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19100.069</t>
+          <t>35754.726</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-25.70</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,17 +2302,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-169.18</t>
+          <t>-283.59</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-85.75</t>
+          <t>-91.66</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1499161354.892341</t>
+          <t>1499662850.984848</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>588369533.0</t>
+          <t>1108572562.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>753461962.0</t>
+          <t>850962782.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1014121978.2</t>
+          <t>944921985.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1826207989.06</t>
+          <t>1839319197.86</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-260660016</t>
+          <t>-93959203</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-180478945.112572</t>
+          <t>-195784246.5206898</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-320340047.87</v>
+        <v>-279963404.27</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36914.823</t>
+          <t>19100.069</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-35.38</t>
+          <t>-25.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-118.78</t>
+          <t>-169.18</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-85.75</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1499161354.892341</t>
+          <t>1499662850.984848</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1140326331.0</t>
+          <t>588369533.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>828070288.4</t>
+          <t>753461962.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1281460447.9</t>
+          <t>1014121978.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1821954460.44</t>
+          <t>1826207989.06</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-453390159</t>
+          <t>-260660016</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-155049653.7024488</t>
+          <t>-180478945.112572</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-310844212.48</v>
+        <v>-320340047.87</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19843.161</t>
+          <t>36914.823</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.61</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-35.38</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-118.78</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-73.71</t>
+          <t>-79.73</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1499161354.892341</t>
+          <t>1499662850.984848</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>624009643.0</t>
+          <t>1140326331.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>881956766.8</t>
+          <t>828070288.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1357437409.7</t>
+          <t>1281460447.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1805702267.22</t>
+          <t>1821954460.44</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-475480642</t>
+          <t>-453390159</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-126723370.2875744</t>
+          <t>-155049653.7024488</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-345315382.7</v>
+        <v>-310844212.48</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24826.953</t>
+          <t>19843.161</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.95</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-42.95</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-63.68</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-68.39</t>
+          <t>-73.71</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1499161354.892341</t>
+          <t>1499662850.984848</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>793535844.0</t>
+          <t>624009643.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>918505887.0</t>
+          <t>881956766.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1610063469.2</t>
+          <t>1357437409.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1809298292.6</t>
+          <t>1805702267.22</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-691557582</t>
+          <t>-475480642</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-86979368.03002107</t>
+          <t>-126723370.2875744</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-326907574.21</v>
+        <v>-345315382.7</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19032.948</t>
+          <t>24826.953</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-43.01</t>
+          <t>-42.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,255 +4046,255 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>32.37</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>33.14</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>31.32</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>30.46</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-63.68</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-68.39</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>1499662850.984848</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>793535844.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>918505887.0</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>1610063469.2</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>1809298292.6</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-691557582</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-86979368.03002107</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-326907574.21</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/09/24</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-8.26</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-11.1876022432316</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-27.53874609309782</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-17.9987389236193</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>42.95</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>5.67%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>22.75</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>C電子產品99.60%、其他0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>仁寶-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>32.5</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>32.65</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.15</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>30.42</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-48.04</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-63.36</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>1499161354.892341</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>621068459.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>1038881188.8</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>1822971879.1</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1803713391.36</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-784090690</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-43356057.81596284</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-307098955.95</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/09/24</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-5.80</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>-11.1876022432316</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-27.53874609309782</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-17.9987389236193</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>4.82</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>42.95</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>19.24</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>5.67%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>23.47</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>128028</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>C電子產品99.60%、其他0.40% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>仁寶-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>30149.028</t>
+          <t>19032.948</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-13.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-48.45</t>
+          <t>-43.01</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>31.24</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>30.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-41.67</t>
+          <t>-48.04</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-58.96</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1499161354.892341</t>
+          <t>1499662850.984848</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>961411165.0</t>
+          <t>621068459.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>1274781994.4</t>
+          <t>1038881188.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>2473123750.7</t>
+          <t>1822971879.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1798901888.5</t>
+          <t>1803713391.36</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1198341756</t>
+          <t>-784090690</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4597196.391051546</t>
+          <t>-43356057.81596284</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-249354461.63</v>
+        <v>-307098955.95</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43281.83</t>
+          <t>30149.028</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-11.36</t>
+          <t>-12.04</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-38.16</t>
+          <t>-48.45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,32 +4903,32 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>32.92</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -4938,127 +4938,127 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-41.67</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-58.96</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>1499662850.984848</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>961411165.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>1274781994.4</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>2473123750.7</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>1798901888.5</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-1198341756</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>4597196.391051546</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-249354461.63</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/09/24</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-6.96</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-54.68</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>1499161354.892341</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>1409758723.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1734850607.4</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>2805199811.8</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1785814116.68</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-1070349204</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>50770225.12228593</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-194422100.32</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/09/24</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-6.23</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24186.087</t>
+          <t>43281.83</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>-12.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.78</t>
+          <t>-5.16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-35.57</t>
+          <t>-38.16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>43019</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>33.84</t>
+          <t>33.41</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>33.16</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.29</t>
+          <t>30.33</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-29.49</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-51.34</t>
+          <t>-54.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1499161354.892341</t>
+          <t>1499662850.984848</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>806755244.0</t>
+          <t>1409758723.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1832918052.6</t>
+          <t>1734850607.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2844796368.0</t>
+          <t>2805199811.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1768788111.4</t>
+          <t>1785814116.68</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1011878315</t>
+          <t>-1070349204</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>95350647.93073882</t>
+          <t>50770225.12228593</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-157040890.37</v>
+        <v>-194422100.32</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>19.24</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>22.75</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>128028</t>
+          <t>126265</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>33.4</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43018.944</t>
+          <t>44692.112</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,57 +1009,57 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>32.23</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-242.93</t>
+          <t>-139.65</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-117.74</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1499662850.984848</t>
+          <t>1500330659.827089</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>974746025.4</t>
+          <t>1118821743.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>901408156.9</t>
+          <t>936141852.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1876762391.38</t>
+          <t>1892720250.14</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>73337868</t>
+          <t>182679890</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-205773457.290989</t>
+          <t>-197125096.3499162</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-189565323.83</v>
+        <v>-149559111.17</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32130.24</t>
+          <t>43018.944</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-591.64</t>
+          <t>-242.93</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.53</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1499662850.984848</t>
+          <t>1500330659.827089</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>956584872.0</t>
+          <t>974746025.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>919270819.4</t>
+          <t>901408156.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1860013080.08</t>
+          <t>1876762391.38</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>37314052</t>
+          <t>73337868</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-208720390.647228</t>
+          <t>-205773457.290989</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-231630863.17</v>
+        <v>-189565323.83</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>33307.957</t>
+          <t>32130.24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-1135.33</t>
+          <t>-591.64</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-97.83</t>
+          <t>-104.53</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1499662850.984848</t>
+          <t>1500330659.827089</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>892390121.6</t>
+          <t>956584872.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>905448004.3</t>
+          <t>919270819.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1847387257.46</t>
+          <t>1860013080.08</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-13057882</t>
+          <t>37314052</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-204554850.1885323</t>
+          <t>-208720390.647228</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-252793170.36</v>
+        <v>-231630863.17</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>35754.726</t>
+          <t>33307.957</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,37 +2322,37 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-283.59</t>
+          <t>-1135.33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>-97.83</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1499662850.984848</t>
+          <t>1500330659.827089</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>850962782.6</t>
+          <t>892390121.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>944921985.7</t>
+          <t>905448004.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1839319197.86</t>
+          <t>1847387257.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-93959203</t>
+          <t>-13057882</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-195784246.5206898</t>
+          <t>-204554850.1885323</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-279963404.27</v>
+        <v>-252793170.36</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19100.069</t>
+          <t>35754.726</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-25.70</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,17 +2733,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-169.18</t>
+          <t>-283.59</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-85.75</t>
+          <t>-91.66</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1499662850.984848</t>
+          <t>1500330659.827089</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>588369533.0</t>
+          <t>1108572562.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>753461962.0</t>
+          <t>850962782.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1014121978.2</t>
+          <t>944921985.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1826207989.06</t>
+          <t>1839319197.86</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-260660016</t>
+          <t>-93959203</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-180478945.112572</t>
+          <t>-195784246.5206898</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-320340047.87</v>
+        <v>-279963404.27</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>36914.823</t>
+          <t>19100.069</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-35.38</t>
+          <t>-25.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-118.78</t>
+          <t>-169.18</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-85.75</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1499662850.984848</t>
+          <t>1500330659.827089</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1140326331.0</t>
+          <t>588369533.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>828070288.4</t>
+          <t>753461962.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1281460447.9</t>
+          <t>1014121978.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1821954460.44</t>
+          <t>1826207989.06</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-453390159</t>
+          <t>-260660016</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-155049653.7024488</t>
+          <t>-180478945.112572</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-310844212.48</v>
+        <v>-320340047.87</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19843.161</t>
+          <t>36914.823</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-35.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-118.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-73.71</t>
+          <t>-79.73</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1499662850.984848</t>
+          <t>1500330659.827089</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>624009643.0</t>
+          <t>1140326331.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>881956766.8</t>
+          <t>828070288.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1357437409.7</t>
+          <t>1281460447.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1805702267.22</t>
+          <t>1821954460.44</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-475480642</t>
+          <t>-453390159</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-126723370.2875744</t>
+          <t>-155049653.7024488</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-345315382.7</v>
+        <v>-310844212.48</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24826.953</t>
+          <t>19843.161</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-42.95</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-63.68</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-68.39</t>
+          <t>-73.71</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1499662850.984848</t>
+          <t>1500330659.827089</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>793535844.0</t>
+          <t>624009643.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>918505887.0</t>
+          <t>881956766.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1610063469.2</t>
+          <t>1357437409.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1809298292.6</t>
+          <t>1805702267.22</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-691557582</t>
+          <t>-475480642</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-86979368.03002107</t>
+          <t>-126723370.2875744</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-326907574.21</v>
+        <v>-345315382.7</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19032.948</t>
+          <t>24826.953</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-13.44</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-43.01</t>
+          <t>-42.95</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,255 +4477,255 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>32.37</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>33.14</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>31.32</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>30.46</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-63.68</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-68.39</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>1500330659.827089</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>793535844.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>918505887.0</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>1610063469.2</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>1809298292.6</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-691557582</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-86979368.03002107</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>-326907574.21</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025/09/24</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-8.26</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>-11.1876022432316</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-27.53874609309782</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-17.9987389236193</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>42.95</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>19.47</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>5.67%</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>22.49</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>129570</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>C電子產品99.60%、其他0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>仁寶-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>32.5</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
           <t>32.65</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>33.15</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>30.42</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-48.04</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-63.36</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>1499662850.984848</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>621068459.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1038881188.8</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>1822971879.1</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1803713391.36</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-784090690</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-43356057.81596284</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-307098955.95</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/09/24</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-5.80</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-11.1876022432316</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-27.53874609309782</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-17.9987389236193</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>42.95</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>18.97</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>5.67%</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>126265</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>C電子產品99.60%、其他0.40% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>仁寶-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30149.028</t>
+          <t>19032.948</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-12.04</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-48.45</t>
+          <t>-43.01</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>31.24</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>30.42</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-41.67</t>
+          <t>-48.04</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-58.96</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1499662850.984848</t>
+          <t>1500330659.827089</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>961411165.0</t>
+          <t>621068459.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>1274781994.4</t>
+          <t>1038881188.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>2473123750.7</t>
+          <t>1822971879.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1798901888.5</t>
+          <t>1803713391.36</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1198341756</t>
+          <t>-784090690</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4597196.391051546</t>
+          <t>-43356057.81596284</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-249354461.63</v>
+        <v>-307098955.95</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43281.83</t>
+          <t>30149.028</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-12.91</t>
+          <t>-9.18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.16</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-38.16</t>
+          <t>-48.45</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>43019</t>
+          <t>44692</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,32 +5334,32 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>33.41</t>
+          <t>32.92</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -5369,127 +5369,127 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.14</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.33</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-41.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-58.96</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>1500330659.827089</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>961411165.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>1274781994.4</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>2473123750.7</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>1798901888.5</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-1198341756</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>4597196.391051546</t>
+        </is>
+      </c>
+      <c r="BC12" t="n">
+        <v>-249354461.63</v>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>2025/09/24</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>-6.96</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-54.68</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>1499662850.984848</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>1409758723.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1734850607.4</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>2805199811.8</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1785814116.68</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-1070349204</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>50770225.12228593</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-194422100.32</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>2025/09/24</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-6.23</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44692.112</t>
+          <t>35199.107</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.27999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-139.65</t>
+          <t>-92.21</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.74</t>
+          <t>-123.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1500330659.827089</t>
+          <t>1500419087.898561</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1118821743.8</t>
+          <t>1105345654.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>936141852.9</t>
+          <t>978154218.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1892720250.14</t>
+          <t>1906340616.66</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>182679890</t>
+          <t>127191435</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-197125096.3499162</t>
+          <t>-188010848.5167454</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-149559111.17</v>
+        <v>-137882485.43</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43018.944</t>
+          <t>44692.112</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,57 +1440,57 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>32.23</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-242.93</t>
+          <t>-139.65</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-117.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1500330659.827089</t>
+          <t>1500419087.898561</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>974746025.4</t>
+          <t>1118821743.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>901408156.9</t>
+          <t>936141852.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1876762391.38</t>
+          <t>1892720250.14</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>73337868</t>
+          <t>182679890</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-205773457.290989</t>
+          <t>-197125096.3499162</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-189565323.83</v>
+        <v>-149559111.17</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32130.24</t>
+          <t>43018.944</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-591.64</t>
+          <t>-242.93</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.53</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1500330659.827089</t>
+          <t>1500419087.898561</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>956584872.0</t>
+          <t>974746025.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>919270819.4</t>
+          <t>901408156.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1860013080.08</t>
+          <t>1876762391.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>37314052</t>
+          <t>73337868</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-208720390.647228</t>
+          <t>-205773457.290989</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-231630863.17</v>
+        <v>-189565323.83</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>33307.957</t>
+          <t>32130.24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,42 +2317,42 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1135.33</t>
+          <t>-591.64</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-97.83</t>
+          <t>-104.53</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1500330659.827089</t>
+          <t>1500419087.898561</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>892390121.6</t>
+          <t>956584872.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>905448004.3</t>
+          <t>919270819.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1847387257.46</t>
+          <t>1860013080.08</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-13057882</t>
+          <t>37314052</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-204554850.1885323</t>
+          <t>-208720390.647228</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-252793170.36</v>
+        <v>-231630863.17</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35754.726</t>
+          <t>33307.957</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,37 +2753,37 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-283.59</t>
+          <t>-1135.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>-97.83</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1500330659.827089</t>
+          <t>1500419087.898561</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>850962782.6</t>
+          <t>892390121.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>944921985.7</t>
+          <t>905448004.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1839319197.86</t>
+          <t>1847387257.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-93959203</t>
+          <t>-13057882</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-195784246.5206898</t>
+          <t>-204554850.1885323</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-279963404.27</v>
+        <v>-252793170.36</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19100.069</t>
+          <t>35754.726</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-25.70</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-169.18</t>
+          <t>-283.59</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-85.75</t>
+          <t>-91.66</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1500330659.827089</t>
+          <t>1500419087.898561</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>588369533.0</t>
+          <t>1108572562.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>753461962.0</t>
+          <t>850962782.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1014121978.2</t>
+          <t>944921985.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1826207989.06</t>
+          <t>1839319197.86</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-260660016</t>
+          <t>-93959203</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-180478945.112572</t>
+          <t>-195784246.5206898</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-320340047.87</v>
+        <v>-279963404.27</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>36914.823</t>
+          <t>19100.069</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-35.38</t>
+          <t>-25.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-118.78</t>
+          <t>-169.18</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-85.75</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1500330659.827089</t>
+          <t>1500419087.898561</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1140326331.0</t>
+          <t>588369533.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>828070288.4</t>
+          <t>753461962.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1281460447.9</t>
+          <t>1014121978.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1821954460.44</t>
+          <t>1826207989.06</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-453390159</t>
+          <t>-260660016</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-155049653.7024488</t>
+          <t>-180478945.112572</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-310844212.48</v>
+        <v>-320340047.87</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19843.161</t>
+          <t>36914.823</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-35.38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-118.78</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-73.71</t>
+          <t>-79.73</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1500330659.827089</t>
+          <t>1500419087.898561</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>624009643.0</t>
+          <t>1140326331.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>881956766.8</t>
+          <t>828070288.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1357437409.7</t>
+          <t>1281460447.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1805702267.22</t>
+          <t>1821954460.44</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-475480642</t>
+          <t>-453390159</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-126723370.2875744</t>
+          <t>-155049653.7024488</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-345315382.7</v>
+        <v>-310844212.48</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24826.953</t>
+          <t>19843.161</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-42.95</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-63.68</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-68.39</t>
+          <t>-73.71</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1500330659.827089</t>
+          <t>1500419087.898561</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>793535844.0</t>
+          <t>624009643.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>918505887.0</t>
+          <t>881956766.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1610063469.2</t>
+          <t>1357437409.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1809298292.6</t>
+          <t>1805702267.22</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-691557582</t>
+          <t>-475480642</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-86979368.03002107</t>
+          <t>-126723370.2875744</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-326907574.21</v>
+        <v>-345315382.7</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19032.948</t>
+          <t>24826.953</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-7.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-43.01</t>
+          <t>-42.95</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,255 +4908,255 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
+          <t>32.37</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>33.14</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>31.32</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>30.46</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>-63.68</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-68.39</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>1500419087.898561</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>793535844.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>918505887.0</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>1610063469.2</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>1809298292.6</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-691557582</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-86979368.03002107</t>
+        </is>
+      </c>
+      <c r="BC11" t="n">
+        <v>-326907574.21</v>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>2025/09/24</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-8.26</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>-11.1876022432316</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-27.53874609309782</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-17.9987389236193</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>42.95</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>19.47</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>5.67%</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>22.92</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>129570</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>C電子產品99.60%、其他0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>仁寶-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>32.5</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>32.65</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>33.15</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>30.42</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>-48.04</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-63.36</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>1500330659.827089</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>621068459.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1038881188.8</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>1822971879.1</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1803713391.36</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-784090690</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-43356057.81596284</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-307098955.95</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>2025/09/24</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-5.80</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-11.1876022432316</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-27.53874609309782</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-17.9987389236193</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>42.95</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>5.67%</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>129570</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>C電子產品99.60%、其他0.40% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>仁寶-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>30149.028</t>
+          <t>19032.948</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.18</t>
+          <t>-10.54</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-4.19</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-48.45</t>
+          <t>-43.01</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>44692</t>
+          <t>35199</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>33.15</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>31.24</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>30.42</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-41.67</t>
+          <t>-48.04</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-58.96</t>
+          <t>-63.36</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1500330659.827089</t>
+          <t>1500419087.898561</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>961411165.0</t>
+          <t>621068459.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>1274781994.4</t>
+          <t>1038881188.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>2473123750.7</t>
+          <t>1822971879.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1798901888.5</t>
+          <t>1803713391.36</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1198341756</t>
+          <t>-784090690</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>4597196.391051546</t>
+          <t>-43356057.81596284</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-249354461.63</v>
+        <v>-307098955.95</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-2.58</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>38787.338</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>28.65</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>35199.107</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>29.4</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.27999999999999</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.59</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-71.88</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.05</t>
+          <t>-128.10</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1500419087.898561</t>
+          <t>1500675497.954741</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1105345654.0</t>
+          <t>1129061877.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>978154218.3</t>
+          <t>1010725999.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1906340616.66</t>
+          <t>1921840103.86</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>127191435</t>
+          <t>118335878</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-188010848.5167454</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-137882485.43</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-177610282.499654</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-120407169.4056509</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>1119253658</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-14.78</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>-16.96</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
-      </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>29.85</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>28.65</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44692.112</t>
+          <t>35199.107</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.27999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-139.65</t>
+          <t>-92.21</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.74</t>
+          <t>-123.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,180 +1540,180 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1500419087.898561</t>
+          <t>1500675497.954741</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1118821743.8</t>
+          <t>1105345654.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>936141852.9</t>
+          <t>978154218.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1892720250.14</t>
+          <t>1906340616.66</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>182679890</t>
+          <t>127191435</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-197125096.3499162</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-149559111.17</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-188010848.5167454</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-137882485.4343059</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>1041192113</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>-14.78</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1713,15 +1723,20 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43018.944</t>
+          <t>44692.112</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,57 +1886,57 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>32.23</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1931,17 +1946,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-242.93</t>
+          <t>-139.65</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-117.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1500419087.898561</t>
+          <t>1500675497.954741</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>974746025.4</t>
+          <t>1118821743.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>901408156.9</t>
+          <t>936141852.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1876762391.38</t>
+          <t>1892720250.14</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>73337868</t>
+          <t>182679890</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-205773457.290989</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-189565323.83</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-197125096.3499162</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-149559111.1740165</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>1308748125</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>-16.96</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>-14.78</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>28.5</t>
-        </is>
-      </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>32130.24</t>
+          <t>43018.944</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2322,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-591.64</t>
+          <t>-242.93</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.53</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,175 +2412,175 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1500419087.898561</t>
+          <t>1500675497.954741</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>956584872.0</t>
+          <t>974746025.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>919270819.4</t>
+          <t>901408156.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1860013080.08</t>
+          <t>1876762391.38</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>37314052</t>
+          <t>73337868</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-208720390.647228</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-231630863.17</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-205773457.290989</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-189565323.8316743</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>1231132098</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-15.80</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>-16.96</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
-      </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2570,20 +2590,25 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>28.65</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33307.957</t>
+          <t>32130.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,42 +2773,42 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2793,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-1135.33</t>
+          <t>-591.64</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-97.83</t>
+          <t>-104.53</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,198 +2848,203 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1500419087.898561</t>
+          <t>1500675497.954741</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>892390121.6</t>
+          <t>956584872.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>905448004.3</t>
+          <t>919270819.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1847387257.46</t>
+          <t>1860013080.08</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-13057882</t>
+          <t>37314052</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-204554850.1885323</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-252793170.36</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-208720390.647228</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-231630863.170054</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>944983395</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-13.33</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>-15.80</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>30.2</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>35754.726</t>
+          <t>33307.957</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,37 +3214,37 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3224,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-283.59</t>
+          <t>-1135.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>-97.83</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,198 +3284,203 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1500419087.898561</t>
+          <t>1500675497.954741</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>850962782.6</t>
+          <t>892390121.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>944921985.7</t>
+          <t>905448004.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1839319197.86</t>
+          <t>1847387257.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-93959203</t>
+          <t>-13057882</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-195784246.5206898</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-279963404.27</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-204554850.1885323</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-252793170.361666</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>1000672539</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>-11.16</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>-13.33</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19100.069</t>
+          <t>35754.726</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-25.70</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-169.18</t>
+          <t>-283.59</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-85.75</t>
+          <t>-91.66</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,198 +3720,203 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1500419087.898561</t>
+          <t>1500675497.954741</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>588369533.0</t>
+          <t>1108572562.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>753461962.0</t>
+          <t>850962782.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1014121978.2</t>
+          <t>944921985.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1826207989.06</t>
+          <t>1839319197.86</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-260660016</t>
+          <t>-93959203</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-180478945.112572</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-320340047.87</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-195784246.5206898</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-279963404.2653377</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>1108572562</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-10.58</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>-11.16</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>36914.823</t>
+          <t>19100.069</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-35.38</t>
+          <t>-25.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-118.78</t>
+          <t>-169.18</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-85.75</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1500419087.898561</t>
+          <t>1500675497.954741</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1140326331.0</t>
+          <t>588369533.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>828070288.4</t>
+          <t>753461962.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1281460447.9</t>
+          <t>1014121978.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1821954460.44</t>
+          <t>1826207989.06</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-453390159</t>
+          <t>-260660016</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-155049653.7024488</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-310844212.48</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-180478945.112572</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-320340047.8682499</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>588369533</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-11.16</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>-10.58</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>30.85</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19843.161</t>
+          <t>36914.823</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-35.38</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-118.78</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-73.71</t>
+          <t>-79.73</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,198 +4592,203 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1500419087.898561</t>
+          <t>1500675497.954741</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>624009643.0</t>
+          <t>1140326331.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>881956766.8</t>
+          <t>828070288.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1357437409.7</t>
+          <t>1281460447.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1805702267.22</t>
+          <t>1821954460.44</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-475480642</t>
+          <t>-453390159</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-126723370.2875744</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-345315382.7</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-155049653.7024488</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-310844212.4842579</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>1140326331</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-8.55</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>-11.16</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24826.953</t>
+          <t>19843.161</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.65</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-42.95</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-63.68</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-68.39</t>
+          <t>-73.71</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1500419087.898561</t>
+          <t>1500675497.954741</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>793535844.0</t>
+          <t>624009643.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>918505887.0</t>
+          <t>881956766.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1610063469.2</t>
+          <t>1357437409.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1809298292.6</t>
+          <t>1805702267.22</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-691557582</t>
+          <t>-475480642</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-86979368.03002107</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-326907574.21</v>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-126723370.2875744</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-345315382.7041175</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>624009643</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-8.26</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>-8.55</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>22.18</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>32.5</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19032.948</t>
+          <t>24826.953</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.54</t>
+          <t>-10.47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-43.01</t>
+          <t>-42.95</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,17 +5374,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>35199</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5339,268 +5394,273 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>32.37</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>33.14</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>31.32</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>30.46</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>-63.68</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-68.39</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>1500675497.954741</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>793535844.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>918505887.0</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>1610063469.2</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>1809298292.6</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-691557582</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-86979368.03002107</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-326907574.2073414</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>793535844</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/09/24</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-8.26</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>仁寶</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-11.1876022432316</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-27.53874609309782</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-17.9987389236193</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>42.95</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>5.67%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>22.18</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>126265</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>C電子產品99.60%、其他0.40% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>仁寶-電腦及週邊設備業-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右下上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>32.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>32.65</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>33.15</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>30.42</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>-48.04</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-63.36</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>1500419087.898561</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>621068459.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1038881188.8</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>1822971879.1</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1803713391.36</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-784090690</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-43356057.81596284</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-307098955.95</v>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>34.5</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>2025/09/24</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>-5.80</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>仁寶</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>-11.1876022432316</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-27.53874609309782</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-17.9987389236193</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>42.95</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>5.67%</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>22.92</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>129570</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>C電子產品99.60%、其他0.40% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>仁寶-電腦及週邊設備業-上市</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右下上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>31.65</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>38787.338</t>
+          <t>41976.404</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>31.59</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>-55.36</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-128.10</t>
+          <t>-132.61</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1500675497.954741</t>
+          <t>1501109161.381636</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1129061877.8</t>
+          <t>1180457053.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1010725999.7</t>
+          <t>1068520962.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1921840103.86</t>
+          <t>1938375533.6</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>118335878</t>
+          <t>111936090</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-177610282.499654</t>
+          <t>-165510446.4190073</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-120407169.4056509</t>
+          <t>-98961347.97545075</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1119253658</v>
+        <v>1201959271</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35199.107</t>
+          <t>38787.338</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.27999999999999</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.59</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-71.88</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.05</t>
+          <t>-128.10</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1500675497.954741</t>
+          <t>1501109161.381636</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1105345654.0</t>
+          <t>1129061877.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>978154218.3</t>
+          <t>1010725999.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1906340616.66</t>
+          <t>1921840103.86</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>127191435</t>
+          <t>118335878</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-188010848.5167454</t>
+          <t>-177610282.499654</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-137882485.4343059</t>
+          <t>-120407169.4056509</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1041192113</v>
+        <v>1119253658</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44692.112</t>
+          <t>35199.107</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.27999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-139.65</t>
+          <t>-92.21</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-117.74</t>
+          <t>-123.05</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1500675497.954741</t>
+          <t>1501109161.381636</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1118821743.8</t>
+          <t>1105345654.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>936141852.9</t>
+          <t>978154218.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1892720250.14</t>
+          <t>1906340616.66</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>182679890</t>
+          <t>127191435</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-197125096.3499162</t>
+          <t>-188010848.5167454</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-149559111.1740165</t>
+          <t>-137882485.4343059</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1308748125</v>
+        <v>1041192113</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43018.944</t>
+          <t>44692.112</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>32.23</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-242.93</t>
+          <t>-139.65</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-117.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1500675497.954741</t>
+          <t>1501109161.381636</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>974746025.4</t>
+          <t>1118821743.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>901408156.9</t>
+          <t>936141852.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1876762391.38</t>
+          <t>1892720250.14</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>73337868</t>
+          <t>182679890</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-205773457.290989</t>
+          <t>-197125096.3499162</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-189565323.8316743</t>
+          <t>-149559111.1740165</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1231132098</v>
+        <v>1308748125</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>32130.24</t>
+          <t>43018.944</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-591.64</t>
+          <t>-242.93</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-104.53</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1500675497.954741</t>
+          <t>1501109161.381636</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>956584872.0</t>
+          <t>974746025.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>919270819.4</t>
+          <t>901408156.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1860013080.08</t>
+          <t>1876762391.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>37314052</t>
+          <t>73337868</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-208720390.647228</t>
+          <t>-205773457.290989</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-231630863.170054</t>
+          <t>-189565323.8316743</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>944983395</v>
+        <v>1231132098</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>33307.957</t>
+          <t>32130.24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,42 +3209,42 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1135.33</t>
+          <t>-591.64</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-97.83</t>
+          <t>-104.53</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1500675497.954741</t>
+          <t>1501109161.381636</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>892390121.6</t>
+          <t>956584872.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>905448004.3</t>
+          <t>919270819.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1847387257.46</t>
+          <t>1860013080.08</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-13057882</t>
+          <t>37314052</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-204554850.1885323</t>
+          <t>-208720390.647228</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-252793170.361666</t>
+          <t>-231630863.170054</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1000672539</v>
+        <v>944983395</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>35754.726</t>
+          <t>33307.957</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-4.18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,37 +3650,37 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-283.59</t>
+          <t>-1135.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>-97.83</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1500675497.954741</t>
+          <t>1501109161.381636</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>850962782.6</t>
+          <t>892390121.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>944921985.7</t>
+          <t>905448004.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1839319197.86</t>
+          <t>1847387257.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-93959203</t>
+          <t>-13057882</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-195784246.5206898</t>
+          <t>-204554850.1885323</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-279963404.2653377</t>
+          <t>-252793170.361666</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1108572562</v>
+        <v>1000672539</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19100.069</t>
+          <t>35754.726</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.70</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,17 +4066,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-169.18</t>
+          <t>-283.59</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-85.75</t>
+          <t>-91.66</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1500675497.954741</t>
+          <t>1501109161.381636</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>588369533.0</t>
+          <t>1108572562.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>753461962.0</t>
+          <t>850962782.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1014121978.2</t>
+          <t>944921985.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1826207989.06</t>
+          <t>1839319197.86</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-260660016</t>
+          <t>-93959203</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-180478945.112572</t>
+          <t>-195784246.5206898</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-320340047.8682499</t>
+          <t>-279963404.2653377</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>588369533</v>
+        <v>1108572562</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>36914.823</t>
+          <t>19100.069</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-35.38</t>
+          <t>-25.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-118.78</t>
+          <t>-169.18</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-85.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1500675497.954741</t>
+          <t>1501109161.381636</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1140326331.0</t>
+          <t>588369533.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>828070288.4</t>
+          <t>753461962.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1281460447.9</t>
+          <t>1014121978.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1821954460.44</t>
+          <t>1826207989.06</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-453390159</t>
+          <t>-260660016</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-155049653.7024488</t>
+          <t>-180478945.112572</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-310844212.4842579</t>
+          <t>-320340047.8682499</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1140326331</v>
+        <v>588369533</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19843.161</t>
+          <t>36914.823</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>-6.79</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-35.38</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-118.78</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-73.71</t>
+          <t>-79.73</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1500675497.954741</t>
+          <t>1501109161.381636</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>624009643.0</t>
+          <t>1140326331.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>881956766.8</t>
+          <t>828070288.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1357437409.7</t>
+          <t>1281460447.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1805702267.22</t>
+          <t>1821954460.44</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-475480642</t>
+          <t>-453390159</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-126723370.2875744</t>
+          <t>-155049653.7024488</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-345315382.7041175</t>
+          <t>-310844212.4842579</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>624009643</v>
+        <v>1140326331</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24826.953</t>
+          <t>19843.161</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.47</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-42.95</t>
+          <t>-35.03</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>33.14</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>31.39</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-63.68</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-68.39</t>
+          <t>-73.71</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1500675497.954741</t>
+          <t>1501109161.381636</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>793535844.0</t>
+          <t>624009643.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>918505887.0</t>
+          <t>881956766.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1610063469.2</t>
+          <t>1357437409.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1809298292.6</t>
+          <t>1805702267.22</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-691557582</t>
+          <t>-475480642</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-86979368.03002107</t>
+          <t>-126723370.2875744</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-326907574.2073414</t>
+          <t>-345315382.7041175</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>793535844</v>
+        <v>624009643</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-8.55</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>22.28</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>126265</t>
+          <t>126485</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41976.404</t>
+          <t>22796.384</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,57 +1014,57 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-55.36</t>
+          <t>-35.41</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-132.61</t>
+          <t>-135.78</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1501109161.381636</t>
+          <t>1500393778.11533</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1180457053.0</t>
+          <t>1067800185.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1068520962.5</t>
+          <t>1021273105.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1938375533.6</t>
+          <t>1938830373.0</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>111936090</t>
+          <t>46527080</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-165510446.4190073</t>
+          <t>-158744778.12761</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-98961347.97545075</t>
+          <t>-121533602.5249245</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>1201959271</v>
+        <v>667847761</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>38787.338</t>
+          <t>41976.404</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>31.59</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>-55.36</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-128.10</t>
+          <t>-132.61</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1501109161.381636</t>
+          <t>1500393778.11533</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1129061877.8</t>
+          <t>1180457053.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1010725999.7</t>
+          <t>1068520962.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1921840103.86</t>
+          <t>1938375533.6</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>118335878</t>
+          <t>111936090</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-177610282.499654</t>
+          <t>-165510446.4190073</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-120407169.4056509</t>
+          <t>-98961347.97545075</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1119253658</v>
+        <v>1201959271</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35199.107</t>
+          <t>38787.338</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.27999999999999</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.59</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-71.88</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.05</t>
+          <t>-128.10</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1501109161.381636</t>
+          <t>1500393778.11533</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1105345654.0</t>
+          <t>1129061877.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>978154218.3</t>
+          <t>1010725999.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1906340616.66</t>
+          <t>1921840103.86</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>127191435</t>
+          <t>118335878</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-188010848.5167454</t>
+          <t>-177610282.499654</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-137882485.4343059</t>
+          <t>-120407169.4056509</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1041192113</v>
+        <v>1119253658</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44692.112</t>
+          <t>35199.107</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.27999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-139.65</t>
+          <t>-92.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.74</t>
+          <t>-123.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1501109161.381636</t>
+          <t>1500393778.11533</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1118821743.8</t>
+          <t>1105345654.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>936141852.9</t>
+          <t>978154218.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1892720250.14</t>
+          <t>1906340616.66</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>182679890</t>
+          <t>127191435</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-197125096.3499162</t>
+          <t>-188010848.5167454</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-149559111.1740165</t>
+          <t>-137882485.4343059</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1308748125</v>
+        <v>1041192113</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,17 +2580,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43018.944</t>
+          <t>44692.112</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,57 +2758,57 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>32.23</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-242.93</t>
+          <t>-139.65</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-117.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1501109161.381636</t>
+          <t>1500393778.11533</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>974746025.4</t>
+          <t>1118821743.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>901408156.9</t>
+          <t>936141852.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1876762391.38</t>
+          <t>1892720250.14</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>73337868</t>
+          <t>182679890</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-205773457.290989</t>
+          <t>-197125096.3499162</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-189565323.8316743</t>
+          <t>-149559111.1740165</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1231132098</v>
+        <v>1308748125</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32130.24</t>
+          <t>43018.944</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-591.64</t>
+          <t>-242.93</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-104.53</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1501109161.381636</t>
+          <t>1500393778.11533</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>956584872.0</t>
+          <t>974746025.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>919270819.4</t>
+          <t>901408156.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1860013080.08</t>
+          <t>1876762391.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>37314052</t>
+          <t>73337868</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-208720390.647228</t>
+          <t>-205773457.290989</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-231630863.170054</t>
+          <t>-189565323.8316743</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>944983395</v>
+        <v>1231132098</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>33307.957</t>
+          <t>32130.24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,42 +3645,42 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -3690,17 +3690,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1135.33</t>
+          <t>-591.64</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-97.83</t>
+          <t>-104.53</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1501109161.381636</t>
+          <t>1500393778.11533</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>892390121.6</t>
+          <t>956584872.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>905448004.3</t>
+          <t>919270819.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1847387257.46</t>
+          <t>1860013080.08</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-13057882</t>
+          <t>37314052</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-204554850.1885323</t>
+          <t>-208720390.647228</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-252793170.361666</t>
+          <t>-231630863.170054</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>1000672539</v>
+        <v>944983395</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>35754.726</t>
+          <t>33307.957</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4086,37 +4086,37 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-283.59</t>
+          <t>-1135.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>-97.83</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1501109161.381636</t>
+          <t>1500393778.11533</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>850962782.6</t>
+          <t>892390121.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>944921985.7</t>
+          <t>905448004.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1839319197.86</t>
+          <t>1847387257.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-93959203</t>
+          <t>-13057882</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-195784246.5206898</t>
+          <t>-204554850.1885323</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-279963404.2653377</t>
+          <t>-252793170.361666</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1108572562</v>
+        <v>1000672539</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19100.069</t>
+          <t>35754.726</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-25.70</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,17 +4502,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-169.18</t>
+          <t>-283.59</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-85.75</t>
+          <t>-91.66</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1501109161.381636</t>
+          <t>1500393778.11533</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>588369533.0</t>
+          <t>1108572562.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>753461962.0</t>
+          <t>850962782.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1014121978.2</t>
+          <t>944921985.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1826207989.06</t>
+          <t>1839319197.86</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-260660016</t>
+          <t>-93959203</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-180478945.112572</t>
+          <t>-195784246.5206898</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-320340047.8682499</t>
+          <t>-279963404.2653377</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>588369533</v>
+        <v>1108572562</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>36914.823</t>
+          <t>19100.069</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.79</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-35.38</t>
+          <t>-25.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-118.78</t>
+          <t>-169.18</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-85.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1501109161.381636</t>
+          <t>1500393778.11533</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1140326331.0</t>
+          <t>588369533.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>828070288.4</t>
+          <t>753461962.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1281460447.9</t>
+          <t>1014121978.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1821954460.44</t>
+          <t>1826207989.06</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-453390159</t>
+          <t>-260660016</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-155049653.7024488</t>
+          <t>-180478945.112572</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-310844212.4842579</t>
+          <t>-320340047.8682499</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1140326331</v>
+        <v>588369533</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19843.161</t>
+          <t>36914.823</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-35.03</t>
+          <t>-35.38</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>41976</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>33.06</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-118.78</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-73.71</t>
+          <t>-79.73</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1501109161.381636</t>
+          <t>1500393778.11533</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>624009643.0</t>
+          <t>1140326331.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>881956766.8</t>
+          <t>828070288.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1357437409.7</t>
+          <t>1281460447.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1805702267.22</t>
+          <t>1821954460.44</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-475480642</t>
+          <t>-453390159</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-126723370.2875744</t>
+          <t>-155049653.7024488</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-345315382.7041175</t>
+          <t>-310844212.4842579</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>624009643</v>
+        <v>1140326331</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-8.55</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>31.15</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22796.384</t>
+          <t>24495.053</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,57 +1014,57 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>30.76</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1074,17 +1074,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-22.35</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-135.78</t>
+          <t>-137.90</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1500393778.11533</t>
+          <t>1499790224.017168</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>1067800185.6</t>
+          <t>949851822.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1021273105.5</t>
+          <t>1034336783.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>1938830373.0</t>
+          <t>1943240864.16</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>46527080</t>
+          <t>-84484960</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-158744778.12761</t>
+          <t>-154393112.1920443</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-121533602.5249245</t>
+          <t>-130458949.546433</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>667847761</v>
+        <v>719006309</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41976.404</t>
+          <t>22796.384</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,57 +1450,57 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>31.26</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-55.36</t>
+          <t>-35.41</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-132.61</t>
+          <t>-135.78</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1500393778.11533</t>
+          <t>1499790224.017168</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1180457053.0</t>
+          <t>1067800185.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1068520962.5</t>
+          <t>1021273105.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>1938375533.6</t>
+          <t>1938830373.0</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>111936090</t>
+          <t>46527080</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-165510446.4190073</t>
+          <t>-158744778.12761</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-98961347.97545075</t>
+          <t>-121533602.5249245</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>1201959271</v>
+        <v>667847761</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1713,17 +1713,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>38787.338</t>
+          <t>41976.404</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>31.59</t>
+          <t>31.26</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>-55.36</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-128.10</t>
+          <t>-132.61</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1500393778.11533</t>
+          <t>1499790224.017168</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>1129061877.8</t>
+          <t>1180457053.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1010725999.7</t>
+          <t>1068520962.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>1921840103.86</t>
+          <t>1938375533.6</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>118335878</t>
+          <t>111936090</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-177610282.499654</t>
+          <t>-165510446.4190073</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-120407169.4056509</t>
+          <t>-98961347.97545075</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>1119253658</v>
+        <v>1201959271</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>35199.107</t>
+          <t>38787.338</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.27999999999999</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.59</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-71.88</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-123.05</t>
+          <t>-128.10</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1500393778.11533</t>
+          <t>1499790224.017168</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>1105345654.0</t>
+          <t>1129061877.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>978154218.3</t>
+          <t>1010725999.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>1906340616.66</t>
+          <t>1921840103.86</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>127191435</t>
+          <t>118335878</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-188010848.5167454</t>
+          <t>-177610282.499654</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-137882485.4343059</t>
+          <t>-120407169.4056509</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>1041192113</v>
+        <v>1119253658</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44692.112</t>
+          <t>35199.107</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.27999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-139.65</t>
+          <t>-92.21</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.74</t>
+          <t>-123.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1500393778.11533</t>
+          <t>1499790224.017168</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>1118821743.8</t>
+          <t>1105345654.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>936141852.9</t>
+          <t>978154218.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>1892720250.14</t>
+          <t>1906340616.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>182679890</t>
+          <t>127191435</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-197125096.3499162</t>
+          <t>-188010848.5167454</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-149559111.1740165</t>
+          <t>-137882485.4343059</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>1308748125</v>
+        <v>1041192113</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2951,12 +2951,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,17 +3016,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43018.944</t>
+          <t>44692.112</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,57 +3194,57 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>32.48</t>
+          <t>32.23</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3254,17 +3254,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-242.93</t>
+          <t>-139.65</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-117.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1500393778.11533</t>
+          <t>1499790224.017168</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>974746025.4</t>
+          <t>1118821743.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>901408156.9</t>
+          <t>936141852.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>1876762391.38</t>
+          <t>1892720250.14</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>73337868</t>
+          <t>182679890</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-205773457.290989</t>
+          <t>-197125096.3499162</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-189565323.8316743</t>
+          <t>-149559111.1740165</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>1231132098</v>
+        <v>1308748125</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>32130.24</t>
+          <t>43018.944</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>32.48</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-591.64</t>
+          <t>-242.93</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-104.53</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1500393778.11533</t>
+          <t>1499790224.017168</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>956584872.0</t>
+          <t>974746025.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>919270819.4</t>
+          <t>901408156.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1860013080.08</t>
+          <t>1876762391.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>37314052</t>
+          <t>73337868</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-208720390.647228</t>
+          <t>-205773457.290989</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-231630863.170054</t>
+          <t>-189565323.8316743</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>944983395</v>
+        <v>1231132098</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33307.957</t>
+          <t>32130.24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,42 +4081,42 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>31.66</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1135.33</t>
+          <t>-591.64</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-97.83</t>
+          <t>-104.53</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1500393778.11533</t>
+          <t>1499790224.017168</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>892390121.6</t>
+          <t>956584872.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>905448004.3</t>
+          <t>919270819.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>1847387257.46</t>
+          <t>1860013080.08</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-13057882</t>
+          <t>37314052</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-204554850.1885323</t>
+          <t>-208720390.647228</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-252793170.361666</t>
+          <t>-231630863.170054</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1000672539</v>
+        <v>944983395</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35754.726</t>
+          <t>33307.957</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4522,37 +4522,37 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>31.56</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -4562,17 +4562,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-283.59</t>
+          <t>-1135.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>-97.83</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1500393778.11533</t>
+          <t>1499790224.017168</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>850962782.6</t>
+          <t>892390121.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>944921985.7</t>
+          <t>905448004.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>1839319197.86</t>
+          <t>1847387257.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-93959203</t>
+          <t>-13057882</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-195784246.5206898</t>
+          <t>-204554850.1885323</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-279963404.2653377</t>
+          <t>-252793170.361666</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1108572562</v>
+        <v>1000672539</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19100.069</t>
+          <t>35754.726</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-25.70</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,17 +4938,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.56</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-169.18</t>
+          <t>-283.59</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-85.75</t>
+          <t>-91.66</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1500393778.11533</t>
+          <t>1499790224.017168</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>588369533.0</t>
+          <t>1108572562.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>753461962.0</t>
+          <t>850962782.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1014121978.2</t>
+          <t>944921985.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>1826207989.06</t>
+          <t>1839319197.86</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-260660016</t>
+          <t>-93959203</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-180478945.112572</t>
+          <t>-195784246.5206898</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-320340047.8682499</t>
+          <t>-279963404.2653377</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>588369533</v>
+        <v>1108572562</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>36914.823</t>
+          <t>19100.069</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-35.38</t>
+          <t>-25.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>24495</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>33.06</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-118.78</t>
+          <t>-169.18</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-79.73</t>
+          <t>-85.75</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1500393778.11533</t>
+          <t>1499790224.017168</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1140326331.0</t>
+          <t>588369533.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>828070288.4</t>
+          <t>753461962.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1281460447.9</t>
+          <t>1014121978.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>1821954460.44</t>
+          <t>1826207989.06</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-453390159</t>
+          <t>-260660016</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-155049653.7024488</t>
+          <t>-180478945.112572</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-310844212.4842579</t>
+          <t>-320340047.8682499</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>1140326331</v>
+        <v>588369533</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>29.16</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>30.76</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>31.83</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>719006309.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>949851822.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>949851822.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1034336783.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1943240864.16</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1943240864.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-130458949.546433</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>719006309</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>719006309.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>29.14</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>31.02</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>31.8</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>667847761.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1067800185.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1067800185.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1021273105.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1938830373.0</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1938830373</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-121533602.5249245</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>667847761</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>667847761.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>31.26</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>31.77</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>31.77</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>1201959271.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1180457053.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1180457053</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1068520962.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1938375533.6</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1938375533.6</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-98961347.97545075</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>1201959271</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1201959271.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>29.03</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>31.59</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>31.76</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>31.76</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>1119253658.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1129061877.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>1129061877.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1010725999.7</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1921840103.86</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1921840103.86</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-120407169.4056509</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>1119253658</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>1119253658.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>29.27999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>31.75</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>1041192113.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1105345654.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1105345654</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>978154218.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1906340616.66</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1906340616.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-137882485.4343059</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>1041192113</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>1041192113.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>29.53</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>32.23</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>31.72</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>32.23</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>31.72</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>1308748125.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1118821743.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1118821743.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>936141852.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1892720250.14</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1892720250.14</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-149559111.1740165</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>1308748125</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1308748125.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>29.82</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>32.48</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>31.69</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>32.48</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>31.69</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1231132098.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>974746025.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>974746025.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>901408156.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1876762391.38</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1876762391.38</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-189565323.8316743</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1231132098</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1231132098.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>30.22</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>32.69</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>31.66</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>31.66</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>944983395.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>956584872.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>956584872</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>919270819.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1860013080.08</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1860013080.08</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-231630863.170054</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>944983395</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>944983395.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>30.72</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>31.62</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>31.62</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1000672539.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>892390121.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>892390121.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>905448004.3</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1847387257.46</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1847387257.46</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-252793170.361666</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1000672539</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1000672539.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>31.07</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>31.56</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>33</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>31.56</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>1108572562.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>850962782.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>850962782.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>944921985.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1839319197.86</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1839319197.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-279963404.2653377</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>1108572562</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>1108572562.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>31.44</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>33.05</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>31.5</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>588369533.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>753461962.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>753461962</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1014121978.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1826207989.06</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1826207989.06</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-320340047.8682499</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>588369533</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>588369533.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24495.053</t>
+          <t>23261.878</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,51 +1014,51 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>24495</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.76</v>
+        <v>30.55</v>
       </c>
       <c r="AN2" t="n">
         <v>31.83</v>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-22.35</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-137.90</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1499790224.017168</t>
+          <t>1499119389.242143</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>949851822.4</v>
+        <v>878974184</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>1034336783.1</t>
+          <t>992159919.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1943240864.16</v>
+        <v>1909839293.42</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-84484960</t>
+          <t>-113185735</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-154393112.1920443</t>
+          <t>-151541925.366011</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-130458949.546433</t>
+          <t>-135860397.8228281</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1261,27 +1261,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22796.384</t>
+          <t>24495.053</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,54 +1444,54 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>24495</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>31.02</v>
+        <v>30.76</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.8</v>
+        <v>31.83</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-22.35</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-135.78</t>
+          <t>-137.90</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1499790224.017168</t>
+          <t>1499119389.242143</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1067800185.6</v>
+        <v>949851822.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1021273105.5</t>
+          <t>1034336783.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1938830373</v>
+        <v>1943240864.16</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>46527080</t>
+          <t>-84484960</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-158744778.12761</t>
+          <t>-154393112.1920443</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-121533602.5249245</t>
+          <t>-130458949.546433</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1691,27 +1691,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,42 +1743,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>2.94</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>22796.384</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>29.55</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>0.17</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>41976.404</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>28.7</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,54 +1874,54 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>24495</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>31.26</v>
+        <v>31.02</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-55.36</t>
+          <t>-35.41</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-132.61</t>
+          <t>-135.78</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1499790224.017168</t>
+          <t>1499119389.242143</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1180457053</v>
+        <v>1067800185.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1068520962.5</t>
+          <t>1021273105.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1938375533.6</v>
+        <v>1938830373</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>111936090</t>
+          <t>46527080</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-165510446.4190073</t>
+          <t>-158744778.12761</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-98961347.97545075</t>
+          <t>-121533602.5249245</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38787.338</t>
+          <t>41976.404</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3.04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>24495</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>31.59</v>
+        <v>31.26</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.76</v>
+        <v>31.77</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>-55.36</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-128.10</t>
+          <t>-132.61</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1499790224.017168</t>
+          <t>1499119389.242143</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1129061877.8</v>
+        <v>1180457053</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1010725999.7</t>
+          <t>1068520962.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1921840103.86</v>
+        <v>1938375533.6</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>118335878</t>
+          <t>111936090</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-177610282.499654</t>
+          <t>-165510446.4190073</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-120407169.4056509</t>
+          <t>-98961347.97545075</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2551,27 +2551,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>35199.107</t>
+          <t>38787.338</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>24495</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.27999999999999</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>31.9</v>
+        <v>31.59</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-71.88</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.05</t>
+          <t>-128.10</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1499790224.017168</t>
+          <t>1499119389.242143</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1105345654</v>
+        <v>1129061877.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>978154218.3</t>
+          <t>1010725999.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1906340616.66</v>
+        <v>1921840103.86</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>127191435</t>
+          <t>118335878</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-188010848.5167454</t>
+          <t>-177610282.499654</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-137882485.4343059</t>
+          <t>-120407169.4056509</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44692.112</t>
+          <t>35199.107</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>24495</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.27999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>32.23</v>
+        <v>31.9</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-139.65</t>
+          <t>-92.21</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-117.74</t>
+          <t>-123.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1499790224.017168</t>
+          <t>1499119389.242143</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1118821743.8</v>
+        <v>1105345654</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>936141852.9</t>
+          <t>978154218.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1892720250.14</v>
+        <v>1906340616.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>182679890</t>
+          <t>127191435</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-197125096.3499162</t>
+          <t>-188010848.5167454</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-149559111.1740165</t>
+          <t>-137882485.4343059</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43018.944</t>
+          <t>44692.112</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,54 +3594,54 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>24495</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>32.48</v>
+        <v>32.23</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.69</v>
+        <v>31.72</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-242.93</t>
+          <t>-139.65</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-117.74</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1499790224.017168</t>
+          <t>1499119389.242143</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>974746025.4</v>
+        <v>1118821743.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>901408156.9</t>
+          <t>936141852.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1876762391.38</v>
+        <v>1892720250.14</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>73337868</t>
+          <t>182679890</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-205773457.290989</t>
+          <t>-197125096.3499162</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-189565323.8316743</t>
+          <t>-149559111.1740165</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3841,27 +3841,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>32130.24</t>
+          <t>43018.944</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>24495</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>32.69</v>
+        <v>32.48</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.66</v>
+        <v>31.69</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-591.64</t>
+          <t>-242.93</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-104.53</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1499790224.017168</t>
+          <t>1499119389.242143</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>956584872</v>
+        <v>974746025.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>919270819.4</t>
+          <t>901408156.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1860013080.08</v>
+        <v>1876762391.38</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>37314052</t>
+          <t>73337868</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-208720390.647228</t>
+          <t>-205773457.290989</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-231630863.170054</t>
+          <t>-189565323.8316743</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4271,27 +4271,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33307.957</t>
+          <t>32130.24</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>24495</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,39 +4469,39 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>32.9</v>
+        <v>32.69</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.62</v>
+        <v>31.66</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1135.33</t>
+          <t>-591.64</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-97.83</t>
+          <t>-104.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1499790224.017168</t>
+          <t>1499119389.242143</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>892390121.6</v>
+        <v>956584872</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>905448004.3</t>
+          <t>919270819.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1847387257.46</v>
+        <v>1860013080.08</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-13057882</t>
+          <t>37314052</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-204554850.1885323</t>
+          <t>-208720390.647228</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-252793170.361666</t>
+          <t>-231630863.170054</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4701,27 +4701,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>35754.726</t>
+          <t>33307.957</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>24495</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,34 +4904,34 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.56</v>
+        <v>31.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-283.59</t>
+          <t>-1135.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>-97.83</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1499790224.017168</t>
+          <t>1499119389.242143</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>850962782.6</v>
+        <v>892390121.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>944921985.7</t>
+          <t>905448004.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1839319197.86</v>
+        <v>1847387257.46</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-93959203</t>
+          <t>-13057882</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-195784246.5206898</t>
+          <t>-204554850.1885323</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-279963404.2653377</t>
+          <t>-252793170.361666</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5131,27 +5131,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19100.069</t>
+          <t>35754.726</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-25.70</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.66</t>
+          <t>-7.26</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.90</t>
+          <t>12.91</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>24495</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-5.86</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>33.05</v>
+        <v>33</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.5</v>
+        <v>31.56</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-169.18</t>
+          <t>-283.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-85.75</t>
+          <t>-91.66</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1499790224.017168</t>
+          <t>1499119389.242143</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>588369533.0</t>
+          <t>1108572562.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>753461962</v>
+        <v>850962782.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1014121978.2</t>
+          <t>944921985.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1826207989.06</v>
+        <v>1839319197.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-260660016</t>
+          <t>-93959203</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-180478945.112572</t>
+          <t>-195784246.5206898</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-320340047.8682499</t>
+          <t>-279963404.2653377</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>588369533.0</t>
+          <t>1108572562.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>130452</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5561,27 +5561,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23261.878</t>
+          <t>11713.05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-21.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.55</v>
+        <v>30.36</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.83</v>
+        <v>31.81</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-139.07</t>
+          <t>-139.72</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1499119389.242143</t>
+          <t>1497718181.257489</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>878974184</v>
+        <v>724039798</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>992159919.0</t>
+          <t>926550837.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1909839293.42</v>
+        <v>1864715623.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-113185735</t>
+          <t>-202511039</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-151541925.366011</t>
+          <t>-153137254.7167376</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-135860397.8228281</t>
+          <t>-161911566.145734</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24495.053</t>
+          <t>23261.878</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,51 +1444,51 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.76</v>
+        <v>30.55</v>
       </c>
       <c r="AN3" t="n">
         <v>31.83</v>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-22.35</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-137.90</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1499119389.242143</t>
+          <t>1497718181.257489</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>949851822.4</v>
+        <v>878974184</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>1034336783.1</t>
+          <t>992159919.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1943240864.16</v>
+        <v>1909839293.42</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-84484960</t>
+          <t>-113185735</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-154393112.1920443</t>
+          <t>-151541925.366011</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-130458949.546433</t>
+          <t>-135860397.8228281</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1691,27 +1691,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22796.384</t>
+          <t>24495.053</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,54 +1874,54 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>31.02</v>
+        <v>30.76</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.8</v>
+        <v>31.83</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-22.35</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-135.78</t>
+          <t>-137.90</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1499119389.242143</t>
+          <t>1497718181.257489</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1067800185.6</v>
+        <v>949851822.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1021273105.5</t>
+          <t>1034336783.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1938830373</v>
+        <v>1943240864.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>46527080</t>
+          <t>-84484960</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-158744778.12761</t>
+          <t>-154393112.1920443</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-121533602.5249245</t>
+          <t>-130458949.546433</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2121,27 +2121,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41976.404</t>
+          <t>22796.384</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,54 +2304,54 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>31.26</v>
+        <v>31.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,17 +2360,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-55.36</t>
+          <t>-35.41</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-132.61</t>
+          <t>-135.78</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1499119389.242143</t>
+          <t>1497718181.257489</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1180457053</v>
+        <v>1067800185.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1068520962.5</t>
+          <t>1021273105.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1938375533.6</v>
+        <v>1938830373</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>111936090</t>
+          <t>46527080</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-165510446.4190073</t>
+          <t>-158744778.12761</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-98961347.97545075</t>
+          <t>-121533602.5249245</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38787.338</t>
+          <t>41976.404</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>31.59</v>
+        <v>31.26</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.76</v>
+        <v>31.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>-55.36</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-128.10</t>
+          <t>-132.61</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1499119389.242143</t>
+          <t>1497718181.257489</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1129061877.8</v>
+        <v>1180457053</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1010725999.7</t>
+          <t>1068520962.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1921840103.86</v>
+        <v>1938375533.6</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>118335878</t>
+          <t>111936090</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-177610282.499654</t>
+          <t>-165510446.4190073</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-120407169.4056509</t>
+          <t>-98961347.97545075</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>35199.107</t>
+          <t>38787.338</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.27999999999999</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>31.9</v>
+        <v>31.59</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-71.88</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-123.05</t>
+          <t>-128.10</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1499119389.242143</t>
+          <t>1497718181.257489</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1105345654</v>
+        <v>1129061877.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>978154218.3</t>
+          <t>1010725999.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1906340616.66</v>
+        <v>1921840103.86</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>127191435</t>
+          <t>118335878</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-188010848.5167454</t>
+          <t>-177610282.499654</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-137882485.4343059</t>
+          <t>-120407169.4056509</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3411,27 +3411,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44692.112</t>
+          <t>35199.107</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.27999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>32.23</v>
+        <v>31.9</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-139.65</t>
+          <t>-92.21</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.74</t>
+          <t>-123.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1499119389.242143</t>
+          <t>1497718181.257489</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1118821743.8</v>
+        <v>1105345654</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>936141852.9</t>
+          <t>978154218.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1892720250.14</v>
+        <v>1906340616.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>182679890</t>
+          <t>127191435</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-197125096.3499162</t>
+          <t>-188010848.5167454</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-149559111.1740165</t>
+          <t>-137882485.4343059</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3841,22 +3841,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43018.944</t>
+          <t>44692.112</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,54 +4024,54 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>32.48</v>
+        <v>32.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.69</v>
+        <v>31.72</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-242.93</t>
+          <t>-139.65</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-117.74</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1499119389.242143</t>
+          <t>1497718181.257489</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>974746025.4</v>
+        <v>1118821743.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>901408156.9</t>
+          <t>936141852.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1876762391.38</v>
+        <v>1892720250.14</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>73337868</t>
+          <t>182679890</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-205773457.290989</t>
+          <t>-197125096.3499162</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-189565323.8316743</t>
+          <t>-149559111.1740165</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4271,27 +4271,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>32130.24</t>
+          <t>43018.944</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>32.69</v>
+        <v>32.48</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.66</v>
+        <v>31.69</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-591.64</t>
+          <t>-242.93</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-104.53</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1499119389.242143</t>
+          <t>1497718181.257489</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>956584872</v>
+        <v>974746025.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>919270819.4</t>
+          <t>901408156.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1860013080.08</v>
+        <v>1876762391.38</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>37314052</t>
+          <t>73337868</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-208720390.647228</t>
+          <t>-205773457.290989</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-231630863.170054</t>
+          <t>-189565323.8316743</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4701,27 +4701,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>33307.957</t>
+          <t>32130.24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,39 +4899,39 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>32.9</v>
+        <v>32.69</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.62</v>
+        <v>31.66</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1135.33</t>
+          <t>-591.64</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-97.83</t>
+          <t>-104.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1499119389.242143</t>
+          <t>1497718181.257489</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>892390121.6</v>
+        <v>956584872</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>905448004.3</t>
+          <t>919270819.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1847387257.46</v>
+        <v>1860013080.08</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-13057882</t>
+          <t>37314052</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-204554850.1885323</t>
+          <t>-208720390.647228</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-252793170.361666</t>
+          <t>-231630863.170054</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5131,27 +5131,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>35754.726</t>
+          <t>33307.957</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.26</t>
+          <t>-9.53</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,34 +5334,34 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.86</t>
+          <t>-6.64</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.56</v>
+        <v>31.62</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-283.59</t>
+          <t>-1135.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-91.66</t>
+          <t>-97.83</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1499119389.242143</t>
+          <t>1497718181.257489</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>850962782.6</v>
+        <v>892390121.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>944921985.7</t>
+          <t>905448004.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1839319197.86</v>
+        <v>1847387257.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-93959203</t>
+          <t>-13057882</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-195784246.5206898</t>
+          <t>-204554850.1885323</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-279963404.2653377</t>
+          <t>-252793170.361666</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1108572562.0</t>
+          <t>1000672539.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.73</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>130452</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5561,27 +5561,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11713.05</t>
+          <t>13724.475</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,37 +1014,37 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,28 +1054,28 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.36</v>
+        <v>30.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-139.72</t>
+          <t>-139.83</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1497718181.257489</t>
+          <t>1496448563.976496</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>724039798</v>
+        <v>564507523.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>926550837.9</t>
+          <t>872482288.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1864715623.88</v>
+        <v>1847497050.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-202511039</t>
+          <t>-307974764</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-153137254.7167376</t>
+          <t>-155980889.6707972</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-161911566.145734</t>
+          <t>-171620881.9181248</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,127 +1313,127 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>11713.05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>23261.878</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-21.86</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-11.20</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>-0.85</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.56</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-11.41</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-10.44</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>8.40</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.55</v>
+        <v>30.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.83</v>
+        <v>31.81</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-139.07</t>
+          <t>-139.72</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1497718181.257489</t>
+          <t>1496448563.976496</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>878974184</v>
+        <v>724039798</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>992159919.0</t>
+          <t>926550837.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1909839293.42</v>
+        <v>1864715623.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-113185735</t>
+          <t>-202511039</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-151541925.366011</t>
+          <t>-153137254.7167376</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-135860397.8228281</t>
+          <t>-161911566.145734</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24495.053</t>
+          <t>23261.878</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,51 +1874,51 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.76</v>
+        <v>30.55</v>
       </c>
       <c r="AN4" t="n">
         <v>31.83</v>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-22.35</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-137.90</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1497718181.257489</t>
+          <t>1496448563.976496</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>949851822.4</v>
+        <v>878974184</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>1034336783.1</t>
+          <t>992159919.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1943240864.16</v>
+        <v>1909839293.42</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-84484960</t>
+          <t>-113185735</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-154393112.1920443</t>
+          <t>-151541925.366011</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-130458949.546433</t>
+          <t>-135860397.8228281</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22796.384</t>
+          <t>24495.053</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,54 +2304,54 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>31.02</v>
+        <v>30.76</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.8</v>
+        <v>31.83</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2360,17 +2360,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-22.35</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-135.78</t>
+          <t>-137.90</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1497718181.257489</t>
+          <t>1496448563.976496</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1067800185.6</v>
+        <v>949851822.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1021273105.5</t>
+          <t>1034336783.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1938830373</v>
+        <v>1943240864.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>46527080</t>
+          <t>-84484960</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-158744778.12761</t>
+          <t>-154393112.1920443</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-121533602.5249245</t>
+          <t>-130458949.546433</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41976.404</t>
+          <t>22796.384</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,54 +2734,54 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>31.26</v>
+        <v>31.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-55.36</t>
+          <t>-35.41</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-132.61</t>
+          <t>-135.78</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1497718181.257489</t>
+          <t>1496448563.976496</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1180457053</v>
+        <v>1067800185.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1068520962.5</t>
+          <t>1021273105.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1938375533.6</v>
+        <v>1938830373</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>111936090</t>
+          <t>46527080</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-165510446.4190073</t>
+          <t>-158744778.12761</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-98961347.97545075</t>
+          <t>-121533602.5249245</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>38787.338</t>
+          <t>41976.404</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>31.59</v>
+        <v>31.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.76</v>
+        <v>31.77</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>-55.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-128.10</t>
+          <t>-132.61</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1497718181.257489</t>
+          <t>1496448563.976496</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1129061877.8</v>
+        <v>1180457053</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1010725999.7</t>
+          <t>1068520962.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1921840103.86</v>
+        <v>1938375533.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>118335878</t>
+          <t>111936090</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-177610282.499654</t>
+          <t>-165510446.4190073</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-120407169.4056509</t>
+          <t>-98961347.97545075</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>35199.107</t>
+          <t>38787.338</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.27999999999999</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>31.9</v>
+        <v>31.59</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-71.88</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.05</t>
+          <t>-128.10</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1497718181.257489</t>
+          <t>1496448563.976496</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1105345654</v>
+        <v>1129061877.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>978154218.3</t>
+          <t>1010725999.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1906340616.66</v>
+        <v>1921840103.86</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>127191435</t>
+          <t>118335878</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-188010848.5167454</t>
+          <t>-177610282.499654</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-137882485.4343059</t>
+          <t>-120407169.4056509</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44692.112</t>
+          <t>35199.107</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.27999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>32.23</v>
+        <v>31.9</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-139.65</t>
+          <t>-92.21</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.74</t>
+          <t>-123.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1497718181.257489</t>
+          <t>1496448563.976496</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1118821743.8</v>
+        <v>1105345654</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>936141852.9</t>
+          <t>978154218.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1892720250.14</v>
+        <v>1906340616.66</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>182679890</t>
+          <t>127191435</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-197125096.3499162</t>
+          <t>-188010848.5167454</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-149559111.1740165</t>
+          <t>-137882485.4343059</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,17 +4276,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43018.944</t>
+          <t>44692.112</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4454,54 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>32.48</v>
+        <v>32.23</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.69</v>
+        <v>31.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,17 +4510,17 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-242.93</t>
+          <t>-139.65</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-117.74</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1497718181.257489</t>
+          <t>1496448563.976496</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>974746025.4</v>
+        <v>1118821743.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>901408156.9</t>
+          <t>936141852.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1876762391.38</v>
+        <v>1892720250.14</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>73337868</t>
+          <t>182679890</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-205773457.290989</t>
+          <t>-197125096.3499162</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-189565323.8316743</t>
+          <t>-149559111.1740165</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>32130.24</t>
+          <t>43018.944</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>32.69</v>
+        <v>32.48</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.66</v>
+        <v>31.69</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-591.64</t>
+          <t>-242.93</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-104.53</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1497718181.257489</t>
+          <t>1496448563.976496</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>956584872</v>
+        <v>974746025.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>919270819.4</t>
+          <t>901408156.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1860013080.08</v>
+        <v>1876762391.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>37314052</t>
+          <t>73337868</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-208720390.647228</t>
+          <t>-205773457.290989</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-231630863.170054</t>
+          <t>-189565323.8316743</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>33307.957</t>
+          <t>32130.24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.53</t>
+          <t>-12.10</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>11.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>13724</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,39 +5329,39 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-6.64</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>32.9</v>
+        <v>32.69</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.62</v>
+        <v>31.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1135.33</t>
+          <t>-591.64</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-97.83</t>
+          <t>-104.53</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1497718181.257489</t>
+          <t>1496448563.976496</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>892390121.6</v>
+        <v>956584872</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>905448004.3</t>
+          <t>919270819.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1847387257.46</v>
+        <v>1860013080.08</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-13057882</t>
+          <t>37314052</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-204554850.1885323</t>
+          <t>-208720390.647228</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-252793170.361666</t>
+          <t>-231630863.170054</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1000672539.0</t>
+          <t>944983395.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.80</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129790</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,127 +883,127 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>13310.128</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-35.41</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-10.74</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>0.34</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>13724.475</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.51</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-35.30</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>-10.89</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-0.51</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.18</v>
+        <v>30.03</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-139.83</t>
+          <t>-139.46</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1496448563.976496</t>
+          <t>1495156877.321479</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>564507523.8</v>
+        <v>509390351</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>872482288.4</t>
+          <t>788595268.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1847497050.12</v>
+        <v>1812926065.04</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-307974764</t>
+          <t>-279204917</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-155980889.6707972</t>
+          <t>-158911457.5884969</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-171620881.9181248</t>
+          <t>-175029581.1358453</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>129790</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11713.05</t>
+          <t>13724.475</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,37 +1444,37 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1484,28 +1484,28 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.36</v>
+        <v>30.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-139.72</t>
+          <t>-139.83</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1496448563.976496</t>
+          <t>1495156877.321479</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>724039798</v>
+        <v>564507523.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>926550837.9</t>
+          <t>872482288.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1864715623.88</v>
+        <v>1847497050.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-202511039</t>
+          <t>-307974764</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-153137254.7167376</t>
+          <t>-155980889.6707972</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-161911566.145734</t>
+          <t>-171620881.9181248</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>129790</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23261.878</t>
+          <t>11713.05</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-21.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.55</v>
+        <v>30.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.83</v>
+        <v>31.81</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.07</t>
+          <t>-139.72</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1496448563.976496</t>
+          <t>1495156877.321479</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>878974184</v>
+        <v>724039798</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>992159919.0</t>
+          <t>926550837.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1909839293.42</v>
+        <v>1864715623.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-113185735</t>
+          <t>-202511039</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-151541925.366011</t>
+          <t>-153137254.7167376</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-135860397.8228281</t>
+          <t>-161911566.145734</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>129790</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24495.053</t>
+          <t>23261.878</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,51 +2304,51 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.76</v>
+        <v>30.55</v>
       </c>
       <c r="AN5" t="n">
         <v>31.83</v>
@@ -2360,17 +2360,17 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-22.35</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-137.90</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1496448563.976496</t>
+          <t>1495156877.321479</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>949851822.4</v>
+        <v>878974184</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>1034336783.1</t>
+          <t>992159919.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1943240864.16</v>
+        <v>1909839293.42</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-84484960</t>
+          <t>-113185735</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-154393112.1920443</t>
+          <t>-151541925.366011</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-130458949.546433</t>
+          <t>-135860397.8228281</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>129790</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22796.384</t>
+          <t>24495.053</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,54 +2734,54 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>31.02</v>
+        <v>30.76</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.8</v>
+        <v>31.83</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-22.35</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-135.78</t>
+          <t>-137.90</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1496448563.976496</t>
+          <t>1495156877.321479</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1067800185.6</v>
+        <v>949851822.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1021273105.5</t>
+          <t>1034336783.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1938830373</v>
+        <v>1943240864.16</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>46527080</t>
+          <t>-84484960</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-158744778.12761</t>
+          <t>-154393112.1920443</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-121533602.5249245</t>
+          <t>-130458949.546433</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>129790</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41976.404</t>
+          <t>22796.384</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,54 +3164,54 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>31.26</v>
+        <v>31.02</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-55.36</t>
+          <t>-35.41</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-132.61</t>
+          <t>-135.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1496448563.976496</t>
+          <t>1495156877.321479</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1180457053</v>
+        <v>1067800185.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1068520962.5</t>
+          <t>1021273105.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1938375533.6</v>
+        <v>1938830373</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>111936090</t>
+          <t>46527080</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-165510446.4190073</t>
+          <t>-158744778.12761</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-98961347.97545075</t>
+          <t>-121533602.5249245</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>129790</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>38787.338</t>
+          <t>41976.404</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>31.59</v>
+        <v>31.26</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.76</v>
+        <v>31.77</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>-55.36</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-128.10</t>
+          <t>-132.61</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1496448563.976496</t>
+          <t>1495156877.321479</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1129061877.8</v>
+        <v>1180457053</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1010725999.7</t>
+          <t>1068520962.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1921840103.86</v>
+        <v>1938375533.6</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>118335878</t>
+          <t>111936090</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-177610282.499654</t>
+          <t>-165510446.4190073</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-120407169.4056509</t>
+          <t>-98961347.97545075</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>129790</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>35199.107</t>
+          <t>38787.338</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.27999999999999</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>31.9</v>
+        <v>31.59</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-71.88</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.05</t>
+          <t>-128.10</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1496448563.976496</t>
+          <t>1495156877.321479</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1105345654</v>
+        <v>1129061877.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>978154218.3</t>
+          <t>1010725999.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1906340616.66</v>
+        <v>1921840103.86</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>127191435</t>
+          <t>118335878</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-188010848.5167454</t>
+          <t>-177610282.499654</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-137882485.4343059</t>
+          <t>-120407169.4056509</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>129790</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44692.112</t>
+          <t>35199.107</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.27999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>32.23</v>
+        <v>31.9</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-139.65</t>
+          <t>-92.21</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.74</t>
+          <t>-123.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1496448563.976496</t>
+          <t>1495156877.321479</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1118821743.8</v>
+        <v>1105345654</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>936141852.9</t>
+          <t>978154218.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1892720250.14</v>
+        <v>1906340616.66</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>182679890</t>
+          <t>127191435</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-197125096.3499162</t>
+          <t>-188010848.5167454</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-149559111.1740165</t>
+          <t>-137882485.4343059</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>129790</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43018.944</t>
+          <t>44692.112</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,54 +4884,54 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>32.48</v>
+        <v>32.23</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.69</v>
+        <v>31.72</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-242.93</t>
+          <t>-139.65</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-117.74</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1496448563.976496</t>
+          <t>1495156877.321479</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>974746025.4</v>
+        <v>1118821743.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>901408156.9</t>
+          <t>936141852.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1876762391.38</v>
+        <v>1892720250.14</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>73337868</t>
+          <t>182679890</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-205773457.290989</t>
+          <t>-197125096.3499162</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-189565323.8316743</t>
+          <t>-149559111.1740165</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>129790</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>32130.24</t>
+          <t>43018.944</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-12.10</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11.60</t>
+          <t>15.54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>32.69</v>
+        <v>32.48</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.66</v>
+        <v>31.69</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-591.64</t>
+          <t>-242.93</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-104.53</t>
+          <t>-111.54</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/21</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1496448563.976496</t>
+          <t>1495156877.321479</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>956584872</v>
+        <v>974746025.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>919270819.4</t>
+          <t>901408156.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1860013080.08</v>
+        <v>1876762391.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>37314052</t>
+          <t>73337868</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-208720390.647228</t>
+          <t>-205773457.290989</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-231630863.170054</t>
+          <t>-189565323.8316743</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>944983395.0</t>
+          <t>1231132098.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.80</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>19.54</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>129790</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13310.128</t>
+          <t>24303.495</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-30.02</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,75 +1014,75 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>30.03</v>
+        <v>29.94</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>-0.64</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
           <t>-0.74</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
       <c r="AS2" t="inlineStr">
         <is>
           <t>1.94</t>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-139.46</t>
+          <t>-138.18</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1495156877.321479</t>
+          <t>1494584909.65483</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>509390351</v>
+        <v>511254641.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>788595268.3</t>
+          <t>730553231.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1812926065.04</v>
+        <v>1804494052.1</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-279204917</t>
+          <t>-219298590</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-158911457.5884969</t>
+          <t>-157207385.8571671</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-175029581.1358453</t>
+          <t>-147834991.3348535</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1261,27 +1261,27 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,14 +1296,14 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,127 +1313,127 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>13310.128</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-35.41</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-10.74</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>0.34</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>13724.475</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-35.30</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-10.89</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.51</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.18</v>
+        <v>30.03</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-139.83</t>
+          <t>-139.46</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1495156877.321479</t>
+          <t>1494584909.65483</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>564507523.8</v>
+        <v>509390351</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>872482288.4</t>
+          <t>788595268.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1847497050.12</v>
+        <v>1812926065.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-307974764</t>
+          <t>-279204917</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-155980889.6707972</t>
+          <t>-158911457.5884969</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-171620881.9181248</t>
+          <t>-175029581.1358453</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11713.05</t>
+          <t>13724.475</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,37 +1874,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1914,28 +1914,28 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.36</v>
+        <v>30.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.72</t>
+          <t>-139.83</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1495156877.321479</t>
+          <t>1494584909.65483</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>724039798</v>
+        <v>564507523.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>926550837.9</t>
+          <t>872482288.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1864715623.88</v>
+        <v>1847497050.12</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-202511039</t>
+          <t>-307974764</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-153137254.7167376</t>
+          <t>-155980889.6707972</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-161911566.145734</t>
+          <t>-171620881.9181248</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2121,27 +2121,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23261.878</t>
+          <t>11713.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-21.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.55</v>
+        <v>30.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.83</v>
+        <v>31.81</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.07</t>
+          <t>-139.72</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1495156877.321479</t>
+          <t>1494584909.65483</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>878974184</v>
+        <v>724039798</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>992159919.0</t>
+          <t>926550837.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1909839293.42</v>
+        <v>1864715623.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-113185735</t>
+          <t>-202511039</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-151541925.366011</t>
+          <t>-153137254.7167376</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-135860397.8228281</t>
+          <t>-161911566.145734</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2561,17 +2561,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24495.053</t>
+          <t>23261.878</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,51 +2734,51 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.76</v>
+        <v>30.55</v>
       </c>
       <c r="AN6" t="n">
         <v>31.83</v>
@@ -2790,17 +2790,17 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-22.35</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-137.90</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1495156877.321479</t>
+          <t>1494584909.65483</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>949851822.4</v>
+        <v>878974184</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>1034336783.1</t>
+          <t>992159919.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1943240864.16</v>
+        <v>1909839293.42</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-84484960</t>
+          <t>-113185735</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-154393112.1920443</t>
+          <t>-151541925.366011</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-130458949.546433</t>
+          <t>-135860397.8228281</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22796.384</t>
+          <t>24495.053</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,54 +3164,54 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>31.02</v>
+        <v>30.76</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.8</v>
+        <v>31.83</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-22.35</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-135.78</t>
+          <t>-137.90</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1495156877.321479</t>
+          <t>1494584909.65483</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1067800185.6</v>
+        <v>949851822.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1021273105.5</t>
+          <t>1034336783.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1938830373</v>
+        <v>1943240864.16</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>46527080</t>
+          <t>-84484960</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-158744778.12761</t>
+          <t>-154393112.1920443</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-121533602.5249245</t>
+          <t>-130458949.546433</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3411,27 +3411,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41976.404</t>
+          <t>22796.384</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,54 +3594,54 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>31.26</v>
+        <v>31.02</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-55.36</t>
+          <t>-35.41</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-132.61</t>
+          <t>-135.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1495156877.321479</t>
+          <t>1494584909.65483</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1180457053</v>
+        <v>1067800185.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1068520962.5</t>
+          <t>1021273105.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1938375533.6</v>
+        <v>1938830373</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>111936090</t>
+          <t>46527080</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-165510446.4190073</t>
+          <t>-158744778.12761</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-98961347.97545075</t>
+          <t>-121533602.5249245</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>38787.338</t>
+          <t>41976.404</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>31.59</v>
+        <v>31.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.76</v>
+        <v>31.77</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>-55.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-128.10</t>
+          <t>-132.61</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1495156877.321479</t>
+          <t>1494584909.65483</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1129061877.8</v>
+        <v>1180457053</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1010725999.7</t>
+          <t>1068520962.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1921840103.86</v>
+        <v>1938375533.6</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>118335878</t>
+          <t>111936090</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-177610282.499654</t>
+          <t>-165510446.4190073</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-120407169.4056509</t>
+          <t>-98961347.97545075</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4271,27 +4271,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,14 +4306,14 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>35199.107</t>
+          <t>38787.338</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.27999999999999</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>31.9</v>
+        <v>31.59</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-71.88</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.05</t>
+          <t>-128.10</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1495156877.321479</t>
+          <t>1494584909.65483</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1105345654</v>
+        <v>1129061877.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>978154218.3</t>
+          <t>1010725999.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1906340616.66</v>
+        <v>1921840103.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>127191435</t>
+          <t>118335878</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-188010848.5167454</t>
+          <t>-177610282.499654</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-137882485.4343059</t>
+          <t>-120407169.4056509</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4701,27 +4701,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44692.112</t>
+          <t>35199.107</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.27999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>32.23</v>
+        <v>31.9</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-139.65</t>
+          <t>-92.21</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.74</t>
+          <t>-123.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1495156877.321479</t>
+          <t>1494584909.65483</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1118821743.8</v>
+        <v>1105345654</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>936141852.9</t>
+          <t>978154218.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1892720250.14</v>
+        <v>1906340616.66</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>182679890</t>
+          <t>127191435</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-197125096.3499162</t>
+          <t>-188010848.5167454</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-149559111.1740165</t>
+          <t>-137882485.4343059</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5131,22 +5131,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43018.944</t>
+          <t>44692.112</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>19.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.54</t>
+          <t>16.14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,54 +5314,54 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>24303</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-8.38</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>32.48</v>
+        <v>32.23</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.69</v>
+        <v>31.72</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5370,17 +5370,17 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-242.93</t>
+          <t>-139.65</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.54</t>
+          <t>-117.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1495156877.321479</t>
+          <t>1494584909.65483</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>974746025.4</v>
+        <v>1118821743.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>901408156.9</t>
+          <t>936141852.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1876762391.38</v>
+        <v>1892720250.14</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>73337868</t>
+          <t>182679890</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-205773457.290989</t>
+          <t>-197125096.3499162</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-189565323.8316743</t>
+          <t>-149559111.1740165</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1231132098.0</t>
+          <t>1308748125.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>19.97</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>26.35</t>
+          <t>26.9</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>130011</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5561,27 +5561,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24303.495</t>
+          <t>16538.526</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-30.02</t>
+          <t>-29.91</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>29.94</v>
+        <v>29.83</v>
       </c>
       <c r="AN2" t="n">
         <v>31.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-138.18</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1494584909.65483</t>
+          <t>1493532208.3</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>511254641.2</v>
+        <v>474217917.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>730553231.8</t>
+          <t>676596050.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1804494052.1</v>
+        <v>1797159838.26</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-219298590</t>
+          <t>-202378133</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-157207385.8571671</t>
+          <t>-154884090.0277241</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-147834991.3348535</t>
+          <t>-142105962.9657878</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13310.128</t>
+          <t>24303.495</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-30.02</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,75 +1444,75 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>30.03</v>
+        <v>29.94</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>-0.64</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
           <t>-0.74</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
       <c r="AS3" t="inlineStr">
         <is>
           <t>1.94</t>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-139.46</t>
+          <t>-138.18</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1494584909.65483</t>
+          <t>1493532208.3</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>509390351</v>
+        <v>511254641.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>788595268.3</t>
+          <t>730553231.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1812926065.04</v>
+        <v>1804494052.1</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-279204917</t>
+          <t>-219298590</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-158911457.5884969</t>
+          <t>-157207385.8571671</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-175029581.1358453</t>
+          <t>-147834991.3348535</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,14 +1726,14 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,127 +1743,127 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>13310.128</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-35.41</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-10.74</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>0.34</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>13724.475</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-35.30</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-10.89</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-0.51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.18</v>
+        <v>30.03</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.83</t>
+          <t>-139.46</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1494584909.65483</t>
+          <t>1493532208.3</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>564507523.8</v>
+        <v>509390351</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>872482288.4</t>
+          <t>788595268.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1847497050.12</v>
+        <v>1812926065.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-307974764</t>
+          <t>-279204917</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-155980889.6707972</t>
+          <t>-158911457.5884969</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-171620881.9181248</t>
+          <t>-175029581.1358453</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11713.05</t>
+          <t>13724.475</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,37 +2304,37 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2344,28 +2344,28 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.36</v>
+        <v>30.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.72</t>
+          <t>-139.83</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1494584909.65483</t>
+          <t>1493532208.3</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>724039798</v>
+        <v>564507523.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>926550837.9</t>
+          <t>872482288.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1864715623.88</v>
+        <v>1847497050.12</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-202511039</t>
+          <t>-307974764</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-153137254.7167376</t>
+          <t>-155980889.6707972</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-161911566.145734</t>
+          <t>-171620881.9181248</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23261.878</t>
+          <t>11713.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,102 +2628,102 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-21.86</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-11.20</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>-0.85</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-11.41</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-10.44</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>8.40</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.55</v>
+        <v>30.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.83</v>
+        <v>31.81</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.07</t>
+          <t>-139.72</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1494584909.65483</t>
+          <t>1493532208.3</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>878974184</v>
+        <v>724039798</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>992159919.0</t>
+          <t>926550837.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1909839293.42</v>
+        <v>1864715623.88</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-113185735</t>
+          <t>-202511039</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-151541925.366011</t>
+          <t>-153137254.7167376</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-135860397.8228281</t>
+          <t>-161911566.145734</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24495.053</t>
+          <t>23261.878</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,51 +3164,51 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.76</v>
+        <v>30.55</v>
       </c>
       <c r="AN7" t="n">
         <v>31.83</v>
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-22.35</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-137.90</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1494584909.65483</t>
+          <t>1493532208.3</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>949851822.4</v>
+        <v>878974184</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>1034336783.1</t>
+          <t>992159919.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1943240864.16</v>
+        <v>1909839293.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-84484960</t>
+          <t>-113185735</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-154393112.1920443</t>
+          <t>-151541925.366011</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-130458949.546433</t>
+          <t>-135860397.8228281</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22796.384</t>
+          <t>24495.053</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,54 +3594,54 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>31.02</v>
+        <v>30.76</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.8</v>
+        <v>31.83</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-22.35</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-135.78</t>
+          <t>-137.90</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1494584909.65483</t>
+          <t>1493532208.3</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1067800185.6</v>
+        <v>949851822.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1021273105.5</t>
+          <t>1034336783.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1938830373</v>
+        <v>1943240864.16</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>46527080</t>
+          <t>-84484960</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-158744778.12761</t>
+          <t>-154393112.1920443</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-121533602.5249245</t>
+          <t>-130458949.546433</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41976.404</t>
+          <t>22796.384</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,54 +4024,54 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.37</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>31.26</v>
+        <v>31.02</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-55.36</t>
+          <t>-35.41</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-132.61</t>
+          <t>-135.78</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1494584909.65483</t>
+          <t>1493532208.3</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1180457053</v>
+        <v>1067800185.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1068520962.5</t>
+          <t>1021273105.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1938375533.6</v>
+        <v>1938830373</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>111936090</t>
+          <t>46527080</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-165510446.4190073</t>
+          <t>-158744778.12761</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-98961347.97545075</t>
+          <t>-121533602.5249245</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4281,17 +4281,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>38787.338</t>
+          <t>41976.404</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>5.59</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>31.59</v>
+        <v>31.26</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.76</v>
+        <v>31.77</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>-55.36</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-128.10</t>
+          <t>-132.61</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1494584909.65483</t>
+          <t>1493532208.3</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1129061877.8</v>
+        <v>1180457053</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1010725999.7</t>
+          <t>1068520962.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1921840103.86</v>
+        <v>1938375533.6</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>118335878</t>
+          <t>111936090</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-177610282.499654</t>
+          <t>-165510446.4190073</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-120407169.4056509</t>
+          <t>-98961347.97545075</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,14 +4736,14 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>35199.107</t>
+          <t>38787.338</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.27999999999999</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>31.9</v>
+        <v>31.59</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-71.88</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-123.05</t>
+          <t>-128.10</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1494584909.65483</t>
+          <t>1493532208.3</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1105345654</v>
+        <v>1129061877.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>978154218.3</t>
+          <t>1010725999.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1906340616.66</v>
+        <v>1921840103.86</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>127191435</t>
+          <t>118335878</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-188010848.5167454</t>
+          <t>-177610282.499654</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-137882485.4343059</t>
+          <t>-120407169.4056509</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44692.112</t>
+          <t>35199.107</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>13.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>12.71</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>24303</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-8.38</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>29.27999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>32.23</v>
+        <v>31.9</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.72</v>
+        <v>31.75</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-139.65</t>
+          <t>-92.21</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.74</t>
+          <t>-123.05</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1494584909.65483</t>
+          <t>1493532208.3</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1118821743.8</v>
+        <v>1105345654</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>936141852.9</t>
+          <t>978154218.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1892720250.14</v>
+        <v>1906340616.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>182679890</t>
+          <t>127191435</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-197125096.3499162</t>
+          <t>-188010848.5167454</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-149559111.1740165</t>
+          <t>-137882485.4343059</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1308748125.0</t>
+          <t>1041192113.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>20.13</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>132875</t>
+          <t>133977</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,17 +5566,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16538.526</t>
+          <t>12666.27</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-29.91</t>
+          <t>-20.07</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>96.49</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
+          <t>96.83</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.66</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>29.83</v>
+        <v>29.76</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>22.90</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.70</t>
-        </is>
+          <t>29.19</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.65</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-136.11</t>
+          <t>-133.66</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1493532208.3</t>
+          <t>1492231697.606941</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>474217917.6</v>
+        <v>482017793.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>676596050.8</t>
+          <t>603028795.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1797159838.26</v>
+        <v>1784609935.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-202378133</t>
+          <t>-121011002</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-154884090.0277241</t>
+          <t>-153116681.3785815</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-142105962.9657878</t>
+          <t>-143395933.8082972</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1263,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1301,11 +1293,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>2324</t>
@@ -1313,12 +1301,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24303.495</t>
+          <t>16538.526</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1316,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1326,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-30.02</t>
+          <t>-29.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1401,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1411,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1432,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,59 +1447,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>91.23</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-1.09</t>
-        </is>
+          <t>96.49</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.2</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>29.94</v>
+        <v>29.83</v>
       </c>
       <c r="AN3" t="n">
         <v>31.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>13.36</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.74</t>
-        </is>
+          <t>22.90</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-0.7</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1500,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-138.18</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1510,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1493532208.3</t>
+          <t>1492231697.606941</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>511254641.2</v>
+        <v>474217917.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>730553231.8</t>
+          <t>676596050.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1804494052.1</v>
+        <v>1797159838.26</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-219298590</t>
+          <t>-202378133</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-157207385.8571671</t>
+          <t>-154884090.0277241</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-147834991.3348535</t>
+          <t>-142105962.9657878</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1566,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1611,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1636,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1651,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1676,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1731,11 +1711,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>2324</t>
@@ -1743,12 +1719,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13310.128</t>
+          <t>24303.495</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1734,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1744,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-30.02</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1829,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1850,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>82.46</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-1.84</t>
-        </is>
+          <t>91.23</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-1.09</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>30.03</v>
+        <v>29.94</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3.76</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.74</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
+          <t>13.36</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0.74</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1918,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-139.46</t>
+          <t>-138.18</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1928,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1493532208.3</t>
+          <t>1492231697.606941</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>509390351</v>
+        <v>511254641.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>788595268.3</t>
+          <t>730553231.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1812926065.04</v>
+        <v>1804494052.1</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-279204917</t>
+          <t>-219298590</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-158911457.5884969</t>
+          <t>-157207385.8571671</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-175029581.1358453</t>
+          <t>-147834991.3348535</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1984,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2029,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2054,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2069,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2094,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2161,11 +2129,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>2324</t>
@@ -2173,127 +2137,127 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>13310.128</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-35.41</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-10.74</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
           <t>0.34</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>13724.475</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>3.12</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-35.30</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-10.89</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-0.51</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2268,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>85.96</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-2.27</t>
-        </is>
+          <t>82.46</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-1.84</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.18</v>
+        <v>30.03</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.78</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.76</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2336,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.83</t>
+          <t>-139.46</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2346,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1493532208.3</t>
+          <t>1492231697.606941</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>564507523.8</v>
+        <v>509390351</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>872482288.4</t>
+          <t>788595268.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1847497050.12</v>
+        <v>1812926065.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-307974764</t>
+          <t>-279204917</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-155980889.6707972</t>
+          <t>-158911457.5884969</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-171620881.9181248</t>
+          <t>-175029581.1358453</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2402,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2447,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2462,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2472,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2487,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,7 +2517,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2527,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2559,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11713.05</t>
+          <t>13724.475</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2574,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2584,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2659,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2669,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,37 +2690,33 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>80.56</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-3.38</t>
-        </is>
+          <t>85.96</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-2.27</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2774,34 +2726,30 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.36</v>
+        <v>30.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-6.51</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.77</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2758,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.72</t>
+          <t>-139.83</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2768,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1493532208.3</t>
+          <t>1492231697.606941</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>724039798</v>
+        <v>564507523.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>926550837.9</t>
+          <t>872482288.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1864715623.88</v>
+        <v>1847497050.12</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-202511039</t>
+          <t>-307974764</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-153137254.7167376</t>
+          <t>-155980889.6707972</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-161911566.145734</t>
+          <t>-171620881.9181248</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2824,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2936,7 +2884,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2894,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2909,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2934,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +2981,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23261.878</t>
+          <t>11713.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +2996,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3006,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-21.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3081,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3091,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3112,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>71.0</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-4.42</t>
-        </is>
+          <t>80.56</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-3.38</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.55</v>
+        <v>30.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.83</v>
+        <v>31.81</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-12.07</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
+          <t>-6.51</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.77</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3180,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.07</t>
+          <t>-139.72</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3190,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1493532208.3</t>
+          <t>1492231697.606941</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>878974184</v>
+        <v>724039798</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>992159919.0</t>
+          <t>926550837.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1909839293.42</v>
+        <v>1864715623.88</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-113185735</t>
+          <t>-202511039</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-151541925.366011</t>
+          <t>-153137254.7167376</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-135860397.8228281</t>
+          <t>-161911566.145734</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3246,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3291,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3306,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3316,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3331,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3421,17 +3361,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3403,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24495.053</t>
+          <t>23261.878</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3418,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3428,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3503,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3513,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,51 +3534,47 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>38.42</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-5.21</t>
-        </is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-4.42</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.76</v>
+        <v>30.55</v>
       </c>
       <c r="AN8" t="n">
         <v>31.83</v>
@@ -3650,18 +3586,14 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-22.35</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.73</t>
-        </is>
+          <t>-12.07</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.76</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3602,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-137.90</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3612,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1493532208.3</t>
+          <t>1492231697.606941</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>949851822.4</v>
+        <v>878974184</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1034336783.1</t>
+          <t>992159919.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1943240864.16</v>
+        <v>1909839293.42</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-84484960</t>
+          <t>-113185735</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-154393112.1920443</t>
+          <t>-151541925.366011</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-130458949.546433</t>
+          <t>-135860397.8228281</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3668,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3796,7 +3728,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3738,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3753,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3778,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3825,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22796.384</t>
+          <t>24495.053</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3840,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3850,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3925,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3935,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,54 +3956,50 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.76</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-6.05</t>
-        </is>
+          <t>38.42</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-5.21</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>31.02</v>
+        <v>30.76</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.8</v>
+        <v>31.83</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4080,18 +4008,14 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-35.41</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.94</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
+          <t>-22.35</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0.73</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4024,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-135.78</t>
+          <t>-137.90</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4034,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1493532208.3</t>
+          <t>1492231697.606941</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1067800185.6</v>
+        <v>949851822.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1021273105.5</t>
+          <t>1034336783.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1938830373</v>
+        <v>1943240864.16</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>46527080</t>
+          <t>-84484960</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-158744778.12761</t>
+          <t>-154393112.1920443</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-121533602.5249245</t>
+          <t>-130458949.546433</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4090,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4135,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4226,7 +4150,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4160,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4175,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4200,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4247,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41976.404</t>
+          <t>22796.384</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4262,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4272,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.59</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4347,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4357,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,54 +4378,50 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.38</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-0.90</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-7.37</t>
-        </is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-6.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>31.26</v>
+        <v>31.02</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4510,18 +4430,14 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-55.36</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
+          <t>-35.41</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4446,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-132.61</t>
+          <t>-135.78</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4456,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1493532208.3</t>
+          <t>1492231697.606941</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1180457053</v>
+        <v>1067800185.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1068520962.5</t>
+          <t>1021273105.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1938375533.6</v>
+        <v>1938830373</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>111936090</t>
+          <t>46527080</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-165510446.4190073</t>
+          <t>-158744778.12761</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-98961347.97545075</t>
+          <t>-121533602.5249245</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4512,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4557,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4567,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4582,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4597,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4711,17 +4627,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4669,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>38787.338</t>
+          <t>41976.404</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4684,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4694,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4769,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4779,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4800,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>16.95</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-1.31</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-8.10</t>
-        </is>
+          <t>9.38</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-7.37</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>31.59</v>
+        <v>31.26</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.76</v>
+        <v>31.77</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-71.88</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.94</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
+          <t>-55.36</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.63</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4868,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-128.10</t>
+          <t>-132.61</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4878,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1493532208.3</t>
+          <t>1492231697.606941</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1129061877.8</v>
+        <v>1180457053</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1010725999.7</t>
+          <t>1068520962.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1921840103.86</v>
+        <v>1938375533.6</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>118335878</t>
+          <t>111936090</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-177610282.499654</t>
+          <t>-165510446.4190073</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-120407169.4056509</t>
+          <t>-98961347.97545075</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4934,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4979,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +4994,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5004,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5019,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5044,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5081,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5091,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>35199.107</t>
+          <t>38787.338</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5106,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5116,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>11.71</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5191,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-13.31</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5201,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.71</t>
+          <t>14.01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5222,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5332,56 +5240,48 @@
           <t>16.95</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-8.23</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-8.1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.27999999999999</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>31.9</v>
+        <v>31.59</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>30.51</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-92.21</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
+          <t>-71.88</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.54</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5290,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-123.05</t>
+          <t>-128.10</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5300,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1493532208.3</t>
+          <t>1492231697.606941</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1105345654</v>
+        <v>1129061877.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>978154218.3</t>
+          <t>1010725999.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1906340616.66</v>
+        <v>1921840103.86</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>127191435</t>
+          <t>118335878</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-188010848.5167454</t>
+          <t>-177610282.499654</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-137882485.4343059</t>
+          <t>-120407169.4056509</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1041192113.0</t>
+          <t>1119253658.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5356,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-16.96</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5401,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5411,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5426,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>20.13</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5441,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>133977</t>
+          <t>133537</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5466,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12666.27</t>
+          <t>19813.327</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-20.07</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1033,47 +1033,47 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.66</v>
+        <v>1.57</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.35</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>30.18</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>29.76</v>
+        <v>29.71</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.74</v>
+        <v>31.73</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.46</v>
+        <v>-0.38</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.65</v>
+        <v>-0.6</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-133.66</t>
+          <t>-130.80</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1492231697.606941</t>
+          <t>1491401306.263791</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>482017793.2</v>
+        <v>521844215.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>603028795.6</t>
+          <t>543175869.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1784609935.56</v>
+        <v>1764344493.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-121011002</t>
+          <t>-21331654</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-153116681.3785815</t>
+          <t>-148671860.7207761</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-143395933.8082972</t>
+          <t>-124225347.1028463</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1293,7 +1293,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2324</t>
@@ -1301,127 +1305,127 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12666.27</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>30.3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>16538.526</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-20.07</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-8.32</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4.57</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>-0.33</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-29.91</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-8.02</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-12-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>5.97</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1432,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>96.83</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>2.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.2</v>
+        <v>0.66</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>29.83</v>
+        <v>29.76</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1500,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-136.11</t>
+          <t>-133.66</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1510,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1492231697.606941</t>
+          <t>1491401306.263791</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>474217917.6</v>
+        <v>482017793.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>676596050.8</t>
+          <t>603028795.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1797159838.26</v>
+        <v>1784609935.56</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-202378133</t>
+          <t>-121011002</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-154884090.0277241</t>
+          <t>-153116681.3785815</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-142105962.9657878</t>
+          <t>-143395933.8082972</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1566,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1626,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1636,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1651,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1681,17 +1685,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1711,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2324</t>
@@ -1719,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24303.495</t>
+          <t>16538.526</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1734,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1744,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-30.02</t>
+          <t>-29.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1819,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1829,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1850,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1865,51 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1.09</v>
+        <v>-0.2</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>29.94</v>
+        <v>29.83</v>
       </c>
       <c r="AN4" t="n">
         <v>31.76</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.64</v>
+        <v>-0.54</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.74</v>
+        <v>-0.7</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1918,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-138.18</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1928,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1492231697.606941</t>
+          <t>1491401306.263791</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>511254641.2</v>
+        <v>474217917.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>730553231.8</t>
+          <t>676596050.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1804494052.1</v>
+        <v>1797159838.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-219298590</t>
+          <t>-202378133</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-157207385.8571671</t>
+          <t>-154884090.0277241</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-147834991.3348535</t>
+          <t>-142105962.9657878</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1984,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2029,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2054,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2069,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2094,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2129,7 +2137,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2324</t>
@@ -2137,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13310.128</t>
+          <t>24303.495</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2152,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2162,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-30.02</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2237,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2247,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2268,67 +2280,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.84</v>
+        <v>-1.09</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>30.03</v>
+        <v>29.94</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AQ5" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="AR5" t="n">
         <v>-0.74</v>
       </c>
-      <c r="AR5" t="n">
-        <v>-0.76</v>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>1.94</t>
@@ -2336,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-139.46</t>
+          <t>-138.18</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2346,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1492231697.606941</t>
+          <t>1491401306.263791</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>509390351</v>
+        <v>511254641.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>788595268.3</t>
+          <t>730553231.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1812926065.04</v>
+        <v>1804494052.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-279204917</t>
+          <t>-219298590</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-158911457.5884969</t>
+          <t>-157207385.8571671</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-175029581.1358453</t>
+          <t>-147834991.3348535</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2402,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2447,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2472,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2487,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2512,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2549,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2559,127 +2571,127 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>13310.128</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-35.41</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>-10.74</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
           <t>0.34</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>13724.475</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-35.30</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-10.89</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>-0.51</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2690,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI6" t="n">
-        <v>-2.27</v>
+        <v>-1.84</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.18</v>
+        <v>30.03</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.78</v>
+        <v>-0.74</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.77</v>
+        <v>-0.76</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2758,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.83</t>
+          <t>-139.46</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2768,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1492231697.606941</t>
+          <t>1491401306.263791</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>564507523.8</v>
+        <v>509390351</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>872482288.4</t>
+          <t>788595268.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1847497050.12</v>
+        <v>1812926065.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-307974764</t>
+          <t>-279204917</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-155980889.6707972</t>
+          <t>-158911457.5884969</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-171620881.9181248</t>
+          <t>-175029581.1358453</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2824,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2869,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2884,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2894,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2909,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2939,7 +2951,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -2949,7 +2961,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2981,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11713.05</t>
+          <t>13724.475</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2996,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3006,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3081,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3091,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3112,33 +3124,33 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AI7" t="n">
-        <v>-3.38</v>
+        <v>-2.27</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3148,27 +3160,27 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.36</v>
+        <v>30.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.82</v>
+        <v>-0.78</v>
       </c>
       <c r="AR7" t="n">
         <v>-0.77</v>
@@ -3180,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.72</t>
+          <t>-139.83</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3190,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1492231697.606941</t>
+          <t>1491401306.263791</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>724039798</v>
+        <v>564507523.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>926550837.9</t>
+          <t>872482288.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1864715623.88</v>
+        <v>1847497050.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-202511039</t>
+          <t>-307974764</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-153137254.7167376</t>
+          <t>-155980889.6707972</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-161911566.145734</t>
+          <t>-171620881.9181248</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3246,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3306,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3316,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3331,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3356,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3403,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23261.878</t>
+          <t>11713.05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3418,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3428,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-21.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3503,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3513,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3534,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.37</v>
+        <v>0.03</v>
       </c>
       <c r="AI8" t="n">
-        <v>-4.42</v>
+        <v>-3.38</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.55</v>
+        <v>30.36</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.83</v>
+        <v>31.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.85</v>
+        <v>-0.82</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.76</v>
+        <v>-0.77</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3602,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.07</t>
+          <t>-139.72</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3612,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1492231697.606941</t>
+          <t>1491401306.263791</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>878974184</v>
+        <v>724039798</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>992159919.0</t>
+          <t>926550837.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1909839293.42</v>
+        <v>1864715623.88</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-113185735</t>
+          <t>-202511039</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-151541925.366011</t>
+          <t>-153137254.7167376</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-135860397.8228281</t>
+          <t>-161911566.145734</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3668,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3713,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3728,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3738,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3753,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3783,17 +3795,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3825,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24495.053</t>
+          <t>23261.878</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3840,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3850,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3925,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3935,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3956,47 +3968,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AI9" t="n">
-        <v>-5.21</v>
+        <v>-4.42</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.76</v>
+        <v>30.55</v>
       </c>
       <c r="AN9" t="n">
         <v>31.83</v>
@@ -4008,14 +4020,14 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-22.35</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.9</v>
+        <v>-0.85</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.73</v>
+        <v>-0.76</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4024,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-137.90</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4034,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1492231697.606941</t>
+          <t>1491401306.263791</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>949851822.4</v>
+        <v>878974184</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>1034336783.1</t>
+          <t>992159919.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1943240864.16</v>
+        <v>1909839293.42</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-84484960</t>
+          <t>-113185735</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-154393112.1920443</t>
+          <t>-151541925.366011</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-130458949.546433</t>
+          <t>-135860397.8228281</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4090,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4150,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4160,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4175,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4200,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4247,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>22796.384</t>
+          <t>24495.053</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4262,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4272,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4347,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4357,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4378,50 +4390,50 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" t="n">
-        <v>-6.05</v>
+        <v>-5.21</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>31.02</v>
+        <v>30.76</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.8</v>
+        <v>31.83</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4430,14 +4442,14 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-22.35</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.73</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4446,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-135.78</t>
+          <t>-137.90</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4456,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1492231697.606941</t>
+          <t>1491401306.263791</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1067800185.6</v>
+        <v>949851822.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1021273105.5</t>
+          <t>1034336783.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1938830373</v>
+        <v>1943240864.16</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>46527080</t>
+          <t>-84484960</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-158744778.12761</t>
+          <t>-154393112.1920443</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-121533602.5249245</t>
+          <t>-130458949.546433</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4512,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4557,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4572,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4582,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4597,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4622,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4669,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>41976.404</t>
+          <t>22796.384</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4684,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4694,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4769,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4779,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4800,50 +4812,50 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.9</v>
+        <v>1.41</v>
       </c>
       <c r="AI11" t="n">
-        <v>-7.37</v>
+        <v>-6.05</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>31.26</v>
+        <v>31.02</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4852,14 +4864,14 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-55.36</t>
+          <t>-35.41</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.98</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.63</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4868,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-132.61</t>
+          <t>-135.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4878,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1492231697.606941</t>
+          <t>1491401306.263791</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1180457053</v>
+        <v>1067800185.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1068520962.5</t>
+          <t>1021273105.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1938375533.6</v>
+        <v>1938830373</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>111936090</t>
+          <t>46527080</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-165510446.4190073</t>
+          <t>-158744778.12761</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-98961347.97545075</t>
+          <t>-121533602.5249245</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4934,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4979,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4989,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5004,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5019,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5049,17 +5061,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5091,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>38787.338</t>
+          <t>41976.404</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5106,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5116,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>10.48</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5191,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.31</t>
+          <t>-13.16</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5201,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.01</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5222,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>19813</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>16.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-1.31</v>
+        <v>-0.9</v>
       </c>
       <c r="AI12" t="n">
-        <v>-8.1</v>
+        <v>-7.37</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>31.59</v>
+        <v>31.26</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.76</v>
+        <v>31.77</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>-55.36</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.98</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.54</v>
+        <v>-0.63</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5290,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-128.10</t>
+          <t>-132.61</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5300,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1492231697.606941</t>
+          <t>1491401306.263791</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1129061877.8</v>
+        <v>1180457053</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1010725999.7</t>
+          <t>1068520962.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1921840103.86</v>
+        <v>1938375533.6</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>118335878</t>
+          <t>111936090</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-177610282.499654</t>
+          <t>-165510446.4190073</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-120407169.4056509</t>
+          <t>-98961347.97545075</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1119253658.0</t>
+          <t>1201959271.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5356,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-16.81</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5401,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5416,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5426,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>20.23</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5441,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.01</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>133537</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5466,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19813.327</t>
+          <t>22852.342</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>96.83</t>
+          <t>75.99</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.23</v>
+        <v>-1.46</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.35</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>29.71</v>
+        <v>29.67</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.73</v>
+        <v>31.63</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-130.80</t>
+          <t>-128.40</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1491401306.263791</t>
+          <t>1490747478.489407</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>521844215.6</v>
+        <v>580524001.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>543175869.7</t>
+          <t>544957176.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1764344493.16</v>
+        <v>1690705225.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-21331654</t>
+          <t>35566825</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-148671860.7207761</t>
+          <t>-141419726.9993428</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-124225347.1028463</t>
+          <t>-101532991.5314595</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12666.27</t>
+          <t>19813.327</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-20.07</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,17 +1436,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1455,47 +1455,47 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.66</v>
+        <v>1.57</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.35</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>30.18</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>29.76</v>
+        <v>29.71</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.74</v>
+        <v>31.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.46</v>
+        <v>-0.38</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.65</v>
+        <v>-0.6</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-133.66</t>
+          <t>-130.80</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1491401306.263791</t>
+          <t>1490747478.489407</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>482017793.2</v>
+        <v>521844215.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>603028795.6</t>
+          <t>543175869.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1784609935.56</v>
+        <v>1764344493.16</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-121011002</t>
+          <t>-21331654</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-153116681.3785815</t>
+          <t>-148671860.7207761</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-143395933.8082972</t>
+          <t>-124225347.1028463</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16538.526</t>
+          <t>12666.27</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-29.91</t>
+          <t>-20.07</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>96.83</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>2.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.2</v>
+        <v>0.66</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>29.83</v>
+        <v>29.76</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-136.11</t>
+          <t>-133.66</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1491401306.263791</t>
+          <t>1490747478.489407</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>474217917.6</v>
+        <v>482017793.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>676596050.8</t>
+          <t>603028795.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1797159838.26</v>
+        <v>1784609935.56</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-202378133</t>
+          <t>-121011002</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-154884090.0277241</t>
+          <t>-153116681.3785815</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-142105962.9657878</t>
+          <t>-143395933.8082972</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24303.495</t>
+          <t>16538.526</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-30.02</t>
+          <t>-29.91</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2295,51 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.09</v>
+        <v>-0.2</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>29.94</v>
+        <v>29.83</v>
       </c>
       <c r="AN5" t="n">
         <v>31.76</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.64</v>
+        <v>-0.54</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.74</v>
+        <v>-0.7</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-138.18</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1491401306.263791</t>
+          <t>1490747478.489407</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>511254641.2</v>
+        <v>474217917.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>730553231.8</t>
+          <t>676596050.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1804494052.1</v>
+        <v>1797159838.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-219298590</t>
+          <t>-202378133</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-157207385.8571671</t>
+          <t>-154884090.0277241</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-147834991.3348535</t>
+          <t>-142105962.9657878</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13310.128</t>
+          <t>24303.495</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-30.02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,67 +2702,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.84</v>
+        <v>-1.09</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>30.03</v>
+        <v>29.94</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AQ6" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="AR6" t="n">
         <v>-0.74</v>
       </c>
-      <c r="AR6" t="n">
-        <v>-0.76</v>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>1.94</t>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-139.46</t>
+          <t>-138.18</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1491401306.263791</t>
+          <t>1490747478.489407</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>509390351</v>
+        <v>511254641.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>788595268.3</t>
+          <t>730553231.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1812926065.04</v>
+        <v>1804494052.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-279204917</t>
+          <t>-219298590</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-158911457.5884969</t>
+          <t>-157207385.8571671</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-175029581.1358453</t>
+          <t>-147834991.3348535</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,127 +2993,127 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>13310.128</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-35.41</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-10.74</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
           <t>0.34</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>13724.475</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-35.30</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-10.89</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>-0.51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI7" t="n">
-        <v>-2.27</v>
+        <v>-1.84</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.18</v>
+        <v>30.03</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.78</v>
+        <v>-0.74</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.77</v>
+        <v>-0.76</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.83</t>
+          <t>-139.46</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1491401306.263791</t>
+          <t>1490747478.489407</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>564507523.8</v>
+        <v>509390351</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>872482288.4</t>
+          <t>788595268.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1847497050.12</v>
+        <v>1812926065.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-307974764</t>
+          <t>-279204917</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-155980889.6707972</t>
+          <t>-158911457.5884969</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-171620881.9181248</t>
+          <t>-175029581.1358453</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11713.05</t>
+          <t>13724.475</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,33 +3546,33 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AI8" t="n">
-        <v>-3.38</v>
+        <v>-2.27</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3582,27 +3582,27 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.36</v>
+        <v>30.18</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.82</v>
+        <v>-0.78</v>
       </c>
       <c r="AR8" t="n">
         <v>-0.77</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.72</t>
+          <t>-139.83</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1491401306.263791</t>
+          <t>1490747478.489407</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>724039798</v>
+        <v>564507523.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>926550837.9</t>
+          <t>872482288.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1864715623.88</v>
+        <v>1847497050.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-202511039</t>
+          <t>-307974764</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-153137254.7167376</t>
+          <t>-155980889.6707972</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-161911566.145734</t>
+          <t>-171620881.9181248</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>23261.878</t>
+          <t>11713.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-21.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.37</v>
+        <v>0.03</v>
       </c>
       <c r="AI9" t="n">
-        <v>-4.42</v>
+        <v>-3.38</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.55</v>
+        <v>30.36</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.83</v>
+        <v>31.81</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.85</v>
+        <v>-0.82</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.76</v>
+        <v>-0.77</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.07</t>
+          <t>-139.72</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1491401306.263791</t>
+          <t>1490747478.489407</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>878974184</v>
+        <v>724039798</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>992159919.0</t>
+          <t>926550837.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1909839293.42</v>
+        <v>1864715623.88</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-113185735</t>
+          <t>-202511039</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-151541925.366011</t>
+          <t>-153137254.7167376</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-135860397.8228281</t>
+          <t>-161911566.145734</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4217,17 +4217,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24495.053</t>
+          <t>23261.878</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,47 +4390,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AI10" t="n">
-        <v>-5.21</v>
+        <v>-4.42</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.76</v>
+        <v>30.55</v>
       </c>
       <c r="AN10" t="n">
         <v>31.83</v>
@@ -4442,14 +4442,14 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-22.35</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.9</v>
+        <v>-0.85</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.73</v>
+        <v>-0.76</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-137.90</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1491401306.263791</t>
+          <t>1490747478.489407</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>949851822.4</v>
+        <v>878974184</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1034336783.1</t>
+          <t>992159919.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1943240864.16</v>
+        <v>1909839293.42</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-84484960</t>
+          <t>-113185735</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-154393112.1920443</t>
+          <t>-151541925.366011</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-130458949.546433</t>
+          <t>-135860397.8228281</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>22796.384</t>
+          <t>24495.053</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,50 +4812,50 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AI11" t="n">
-        <v>-6.05</v>
+        <v>-5.21</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>31.02</v>
+        <v>30.76</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.8</v>
+        <v>31.83</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-22.35</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.73</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-135.78</t>
+          <t>-137.90</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1491401306.263791</t>
+          <t>1490747478.489407</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1067800185.6</v>
+        <v>949851822.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1021273105.5</t>
+          <t>1034336783.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1938830373</v>
+        <v>1943240864.16</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>46527080</t>
+          <t>-84484960</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-158744778.12761</t>
+          <t>-154393112.1920443</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-121533602.5249245</t>
+          <t>-130458949.546433</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>41976.404</t>
+          <t>22796.384</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10.48</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.16</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,50 +5234,50 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>130</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>22852</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>15.76</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.9</v>
+        <v>1.41</v>
       </c>
       <c r="AI12" t="n">
-        <v>-7.37</v>
+        <v>-6.05</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-2.47</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.14</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>31.26</v>
+        <v>31.02</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.77</v>
+        <v>31.8</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5286,14 +5286,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-55.36</t>
+          <t>-35.41</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.98</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.63</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-132.61</t>
+          <t>-135.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1491401306.263791</t>
+          <t>1490747478.489407</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1180457053</v>
+        <v>1067800185.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1068520962.5</t>
+          <t>1021273105.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1938375533.6</v>
+        <v>1938830373</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>111936090</t>
+          <t>46527080</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-165510446.4190073</t>
+          <t>-158744778.12761</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-98961347.97545075</t>
+          <t>-121533602.5249245</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1201959271.0</t>
+          <t>667847761.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-16.81</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>19.74</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27.01</t>
+          <t>27.02</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>134638</t>
+          <t>131333</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5483,17 +5483,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22852.342</t>
+          <t>17565.623</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>75.99</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.46</v>
+        <v>-0.83</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>29.67</v>
+        <v>29.62</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.63</v>
+        <v>31.5</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>33.37</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.55</v>
+        <v>-0.51</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-128.40</t>
+          <t>-126.21</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1490747478.489407</t>
+          <t>1489760695.783498</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>685660828.0</t>
+          <t>527412360.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>580524001.8</v>
+        <v>540340921.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>544957176.4</t>
+          <t>525797781.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1690705225.18</v>
+        <v>1500057523.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>35566825</t>
+          <t>14543140</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-141419726.9993428</t>
+          <t>-134274946.3753211</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-101532991.5314595</t>
+          <t>-94978652.94320226</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>685660828.0</t>
+          <t>527412360.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>-13.19</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19813.327</t>
+          <t>22852.342</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>96.83</t>
+          <t>75.99</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>1.23</v>
+        <v>-1.46</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.35</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>29.71</v>
+        <v>29.67</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.73</v>
+        <v>31.63</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-130.80</t>
+          <t>-128.40</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1490747478.489407</t>
+          <t>1489760695.783498</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>521844215.6</v>
+        <v>580524001.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>543175869.7</t>
+          <t>544957176.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1764344493.16</v>
+        <v>1690705225.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-21331654</t>
+          <t>35566825</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-148671860.7207761</t>
+          <t>-141419726.9993428</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-124225347.1028463</t>
+          <t>-101532991.5314595</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12666.27</t>
+          <t>19813.327</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-20.07</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,17 +1858,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1877,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.66</v>
+        <v>1.57</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.35</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>30.18</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>29.76</v>
+        <v>29.71</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.74</v>
+        <v>31.73</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.46</v>
+        <v>-0.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.65</v>
+        <v>-0.6</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-133.66</t>
+          <t>-130.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1490747478.489407</t>
+          <t>1489760695.783498</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>482017793.2</v>
+        <v>521844215.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>603028795.6</t>
+          <t>543175869.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1784609935.56</v>
+        <v>1764344493.16</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-121011002</t>
+          <t>-21331654</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-153116681.3785815</t>
+          <t>-148671860.7207761</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-143395933.8082972</t>
+          <t>-124225347.1028463</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16538.526</t>
+          <t>12666.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-29.91</t>
+          <t>-20.07</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>96.83</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>2.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.2</v>
+        <v>0.66</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>29.83</v>
+        <v>29.76</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-136.11</t>
+          <t>-133.66</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1490747478.489407</t>
+          <t>1489760695.783498</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>474217917.6</v>
+        <v>482017793.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>676596050.8</t>
+          <t>603028795.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1797159838.26</v>
+        <v>1784609935.56</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-202378133</t>
+          <t>-121011002</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-154884090.0277241</t>
+          <t>-153116681.3785815</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-142105962.9657878</t>
+          <t>-143395933.8082972</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24303.495</t>
+          <t>16538.526</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-30.02</t>
+          <t>-29.91</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2717,51 +2717,51 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AI6" t="n">
-        <v>-1.09</v>
+        <v>-0.2</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>29.94</v>
+        <v>29.83</v>
       </c>
       <c r="AN6" t="n">
         <v>31.76</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.64</v>
+        <v>-0.54</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.74</v>
+        <v>-0.7</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-138.18</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1490747478.489407</t>
+          <t>1489760695.783498</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>511254641.2</v>
+        <v>474217917.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>730553231.8</t>
+          <t>676596050.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1804494052.1</v>
+        <v>1797159838.26</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-219298590</t>
+          <t>-202378133</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-157207385.8571671</t>
+          <t>-154884090.0277241</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-147834991.3348535</t>
+          <t>-142105962.9657878</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13310.128</t>
+          <t>24303.495</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-30.02</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,67 +3124,67 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.84</v>
+        <v>-1.09</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>30.03</v>
+        <v>29.94</v>
       </c>
       <c r="AN7" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AQ7" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="AR7" t="n">
         <v>-0.74</v>
       </c>
-      <c r="AR7" t="n">
-        <v>-0.76</v>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>1.94</t>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-139.46</t>
+          <t>-138.18</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1490747478.489407</t>
+          <t>1489760695.783498</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>509390351</v>
+        <v>511254641.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>788595268.3</t>
+          <t>730553231.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1812926065.04</v>
+        <v>1804494052.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-279204917</t>
+          <t>-219298590</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-158911457.5884969</t>
+          <t>-157207385.8571671</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-175029581.1358453</t>
+          <t>-147834991.3348535</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,127 +3415,127 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>13310.128</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.97</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-35.41</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-10.74</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
           <t>0.34</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>13724.475</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.17</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-35.30</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-10.89</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>-0.51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.27</v>
+        <v>-1.84</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.18</v>
+        <v>30.03</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.78</v>
+        <v>-0.74</v>
       </c>
       <c r="AR8" t="n">
-        <v>-0.77</v>
+        <v>-0.76</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.83</t>
+          <t>-139.46</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1490747478.489407</t>
+          <t>1489760695.783498</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>564507523.8</v>
+        <v>509390351</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>872482288.4</t>
+          <t>788595268.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1847497050.12</v>
+        <v>1812926065.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-307974764</t>
+          <t>-279204917</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-155980889.6707972</t>
+          <t>-158911457.5884969</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-171620881.9181248</t>
+          <t>-175029581.1358453</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11713.05</t>
+          <t>13724.475</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,33 +3968,33 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AI9" t="n">
-        <v>-3.38</v>
+        <v>-2.27</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4004,27 +4004,27 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.36</v>
+        <v>30.18</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.82</v>
+        <v>-0.78</v>
       </c>
       <c r="AR9" t="n">
         <v>-0.77</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.72</t>
+          <t>-139.83</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1490747478.489407</t>
+          <t>1489760695.783498</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>724039798</v>
+        <v>564507523.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>926550837.9</t>
+          <t>872482288.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1864715623.88</v>
+        <v>1847497050.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-202511039</t>
+          <t>-307974764</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-153137254.7167376</t>
+          <t>-155980889.6707972</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-161911566.145734</t>
+          <t>-171620881.9181248</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23261.878</t>
+          <t>11713.05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-21.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.37</v>
+        <v>0.03</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.42</v>
+        <v>-3.38</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.55</v>
+        <v>30.36</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.83</v>
+        <v>31.81</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.85</v>
+        <v>-0.82</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.76</v>
+        <v>-0.77</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-139.07</t>
+          <t>-139.72</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1490747478.489407</t>
+          <t>1489760695.783498</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>878974184</v>
+        <v>724039798</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>992159919.0</t>
+          <t>926550837.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1909839293.42</v>
+        <v>1864715623.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-113185735</t>
+          <t>-202511039</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-151541925.366011</t>
+          <t>-153137254.7167376</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-135860397.8228281</t>
+          <t>-161911566.145734</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4639,17 +4639,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24495.053</t>
+          <t>23261.878</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,47 +4812,47 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AI11" t="n">
-        <v>-5.21</v>
+        <v>-4.42</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.76</v>
+        <v>30.55</v>
       </c>
       <c r="AN11" t="n">
         <v>31.83</v>
@@ -4864,14 +4864,14 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-22.35</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.9</v>
+        <v>-0.85</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.73</v>
+        <v>-0.76</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-137.90</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1490747478.489407</t>
+          <t>1489760695.783498</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>949851822.4</v>
+        <v>878974184</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1034336783.1</t>
+          <t>992159919.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1943240864.16</v>
+        <v>1909839293.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-84484960</t>
+          <t>-113185735</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-154393112.1920443</t>
+          <t>-151541925.366011</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-130458949.546433</t>
+          <t>-135860397.8228281</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22796.384</t>
+          <t>24495.053</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.74</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,50 +5234,50 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>22852</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>38.42</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" t="n">
-        <v>-6.05</v>
+        <v>-5.21</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.14</t>
+          <t>29.16</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>31.02</v>
+        <v>30.76</v>
       </c>
       <c r="AN12" t="n">
-        <v>31.8</v>
+        <v>31.83</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5286,14 +5286,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-22.35</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.73</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-135.78</t>
+          <t>-137.90</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1490747478.489407</t>
+          <t>1489760695.783498</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1067800185.6</v>
+        <v>949851822.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1021273105.5</t>
+          <t>1034336783.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1938830373</v>
+        <v>1943240864.16</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>46527080</t>
+          <t>-84484960</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-158744778.12761</t>
+          <t>-154393112.1920443</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-121533602.5249245</t>
+          <t>-130458949.546433</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>667847761.0</t>
+          <t>719006309.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>19.83</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>131333</t>
+          <t>131994</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17565.623</t>
+          <t>13313.072</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.83</v>
+        <v>-0.8</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>29.62</v>
+        <v>29.58</v>
       </c>
       <c r="AN2" t="n">
-        <v>31.5</v>
+        <v>31.43</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="AR2" t="n">
-        <v>-0.51</v>
+        <v>-0.47</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-126.21</t>
+          <t>-124.30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1489760695.783498</t>
+          <t>1488501458.617606</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>527412360.0</t>
+          <t>397134872.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>540340921.8</v>
+        <v>519443835.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>525797781.5</t>
+          <t>496830876.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1500057523.4</v>
+        <v>1422941594.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>14543140</t>
+          <t>22612959</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-134274946.3753211</t>
+          <t>-128661410.195709</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-94978652.94320226</t>
+          <t>-97786961.20784211</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>527412360.0</t>
+          <t>397134872.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-13.19</t>
+          <t>-13.48</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22852.342</t>
+          <t>17565.623</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>75.99</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.46</v>
+        <v>-0.83</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>29.67</v>
+        <v>29.62</v>
       </c>
       <c r="AN3" t="n">
-        <v>31.63</v>
+        <v>31.5</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>33.37</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.55</v>
+        <v>-0.51</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-128.40</t>
+          <t>-126.21</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>1489760695.783498</t>
+          <t>1488501458.617606</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>685660828.0</t>
+          <t>527412360.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>580524001.8</v>
+        <v>540340921.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>544957176.4</t>
+          <t>525797781.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1690705225.18</v>
+        <v>1500057523.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>35566825</t>
+          <t>14543140</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-141419726.9993428</t>
+          <t>-134274946.3753211</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-101532991.5314595</t>
+          <t>-94978652.94320226</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>685660828.0</t>
+          <t>527412360.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>-13.19</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19813.327</t>
+          <t>22852.342</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>96.83</t>
+          <t>75.99</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.23</v>
+        <v>-1.46</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.35</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>29.71</v>
+        <v>29.67</v>
       </c>
       <c r="AN4" t="n">
-        <v>31.73</v>
+        <v>31.63</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-130.80</t>
+          <t>-128.40</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>1489760695.783498</t>
+          <t>1488501458.617606</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>521844215.6</v>
+        <v>580524001.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>543175869.7</t>
+          <t>544957176.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1764344493.16</v>
+        <v>1690705225.18</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-21331654</t>
+          <t>35566825</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-148671860.7207761</t>
+          <t>-141419726.9993428</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-124225347.1028463</t>
+          <t>-101532991.5314595</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12666.27</t>
+          <t>19813.327</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-20.07</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,17 +2280,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.66</v>
+        <v>1.57</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.35</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>30.18</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>29.76</v>
+        <v>29.71</v>
       </c>
       <c r="AN5" t="n">
-        <v>31.74</v>
+        <v>31.73</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.46</v>
+        <v>-0.38</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.65</v>
+        <v>-0.6</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-133.66</t>
+          <t>-130.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>1489760695.783498</t>
+          <t>1488501458.617606</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>482017793.2</v>
+        <v>521844215.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>603028795.6</t>
+          <t>543175869.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1784609935.56</v>
+        <v>1764344493.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-121011002</t>
+          <t>-21331654</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-153116681.3785815</t>
+          <t>-148671860.7207761</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-143395933.8082972</t>
+          <t>-124225347.1028463</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16538.526</t>
+          <t>12666.27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-29.91</t>
+          <t>-20.07</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>96.83</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>2.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.2</v>
+        <v>0.66</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>29.83</v>
+        <v>29.76</v>
       </c>
       <c r="AN6" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-136.11</t>
+          <t>-133.66</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>1489760695.783498</t>
+          <t>1488501458.617606</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>474217917.6</v>
+        <v>482017793.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>676596050.8</t>
+          <t>603028795.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1797159838.26</v>
+        <v>1784609935.56</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-202378133</t>
+          <t>-121011002</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-154884090.0277241</t>
+          <t>-153116681.3785815</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-142105962.9657878</t>
+          <t>-143395933.8082972</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24303.495</t>
+          <t>16538.526</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-30.02</t>
+          <t>-29.91</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.09</v>
+        <v>-0.2</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>29.94</v>
+        <v>29.83</v>
       </c>
       <c r="AN7" t="n">
         <v>31.76</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.64</v>
+        <v>-0.54</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.74</v>
+        <v>-0.7</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-138.18</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>1489760695.783498</t>
+          <t>1488501458.617606</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>511254641.2</v>
+        <v>474217917.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>730553231.8</t>
+          <t>676596050.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1804494052.1</v>
+        <v>1797159838.26</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-219298590</t>
+          <t>-202378133</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-157207385.8571671</t>
+          <t>-154884090.0277241</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-147834991.3348535</t>
+          <t>-142105962.9657878</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13310.128</t>
+          <t>24303.495</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-30.02</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,67 +3546,67 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.84</v>
+        <v>-1.09</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>30.03</v>
+        <v>29.94</v>
       </c>
       <c r="AN8" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AQ8" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="AR8" t="n">
         <v>-0.74</v>
       </c>
-      <c r="AR8" t="n">
-        <v>-0.76</v>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>1.94</t>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-139.46</t>
+          <t>-138.18</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>1489760695.783498</t>
+          <t>1488501458.617606</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>509390351</v>
+        <v>511254641.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>788595268.3</t>
+          <t>730553231.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1812926065.04</v>
+        <v>1804494052.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-279204917</t>
+          <t>-219298590</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-158911457.5884969</t>
+          <t>-157207385.8571671</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-175029581.1358453</t>
+          <t>-147834991.3348535</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,127 +3837,127 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>13310.128</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-35.41</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-10.74</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
           <t>0.34</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>13724.475</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-0.97</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-35.30</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-10.89</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>-0.51</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.27</v>
+        <v>-1.84</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>30.18</v>
+        <v>30.03</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.78</v>
+        <v>-0.74</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.77</v>
+        <v>-0.76</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-139.83</t>
+          <t>-139.46</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>1489760695.783498</t>
+          <t>1488501458.617606</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>564507523.8</v>
+        <v>509390351</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>872482288.4</t>
+          <t>788595268.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1847497050.12</v>
+        <v>1812926065.04</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-307974764</t>
+          <t>-279204917</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-155980889.6707972</t>
+          <t>-158911457.5884969</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-171620881.9181248</t>
+          <t>-175029581.1358453</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11713.05</t>
+          <t>13724.475</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,33 +4390,33 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.38</v>
+        <v>-2.27</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4426,27 +4426,27 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>30.36</v>
+        <v>30.18</v>
       </c>
       <c r="AN10" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.82</v>
+        <v>-0.78</v>
       </c>
       <c r="AR10" t="n">
         <v>-0.77</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-139.72</t>
+          <t>-139.83</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>1489760695.783498</t>
+          <t>1488501458.617606</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>724039798</v>
+        <v>564507523.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>926550837.9</t>
+          <t>872482288.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1864715623.88</v>
+        <v>1847497050.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-202511039</t>
+          <t>-307974764</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-153137254.7167376</t>
+          <t>-155980889.6707972</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-161911566.145734</t>
+          <t>-171620881.9181248</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23261.878</t>
+          <t>11713.05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-21.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.40</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.37</v>
+        <v>0.03</v>
       </c>
       <c r="AI11" t="n">
-        <v>-4.42</v>
+        <v>-3.38</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.34</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>30.55</v>
+        <v>30.36</v>
       </c>
       <c r="AN11" t="n">
-        <v>31.83</v>
+        <v>31.81</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.07</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.85</v>
+        <v>-0.82</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.76</v>
+        <v>-0.77</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-139.07</t>
+          <t>-139.72</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1489760695.783498</t>
+          <t>1488501458.617606</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>878974184</v>
+        <v>724039798</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>992159919.0</t>
+          <t>926550837.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1909839293.42</v>
+        <v>1864715623.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-113185735</t>
+          <t>-202511039</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-151541925.366011</t>
+          <t>-153137254.7167376</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-135860397.8228281</t>
+          <t>-161911566.145734</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>686803921.0</t>
+          <t>344581728.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-14.20</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5061,17 +5061,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24495.053</t>
+          <t>23261.878</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,47 +5234,47 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>38.42</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5.21</v>
+        <v>-4.42</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-4.02</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>30.76</v>
+        <v>30.55</v>
       </c>
       <c r="AN12" t="n">
         <v>31.83</v>
@@ -5286,14 +5286,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-22.35</t>
+          <t>-12.07</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.9</v>
+        <v>-0.85</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.73</v>
+        <v>-0.76</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-137.90</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1489760695.783498</t>
+          <t>1488501458.617606</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>949851822.4</v>
+        <v>878974184</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1034336783.1</t>
+          <t>992159919.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1943240864.16</v>
+        <v>1909839293.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-84484960</t>
+          <t>-113185735</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-154393112.1920443</t>
+          <t>-151541925.366011</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-130458949.546433</t>
+          <t>-135860397.8228281</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>719006309.0</t>
+          <t>686803921.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-14.20</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.83</t>
+          <t>19.77</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>131994</t>
+          <t>131553</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9910.283</t>
+          <t>18565.916</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,66 +1094,66 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>29.58</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>0.03</v>
+        <v>-1.51</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.51</v>
+        <v>0.65</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>29.59</v>
+        <v>29.61</v>
       </c>
       <c r="AV2" t="n">
-        <v>31.38</v>
+        <v>31.34</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-122.44</t>
+          <t>-121.23</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1487034629.240506</t>
+          <t>1486100140.360955</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>297057181.0</t>
+          <t>547785698.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>502139050.6</v>
+        <v>491010187.8</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>492078421.9</t>
+          <t>506427201.7</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>1372618684.42</v>
+        <v>1331487163.14</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>10060628</t>
+          <t>-15417013</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-124992567.0560451</t>
+          <t>-119348759.9357663</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-104813929.787894</t>
+          <t>-88307820.77423298</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>297057181.0</t>
+          <t>547785698.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1333,27 +1333,27 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13313.072</t>
+          <t>9910.283</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,66 +1556,66 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>-0.8</v>
+        <v>0.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>29.58</v>
+        <v>29.59</v>
       </c>
       <c r="AV3" t="n">
-        <v>31.43</v>
+        <v>31.38</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>33.17</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>-0.32</v>
+        <v>-0.29</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.47</v>
+        <v>-0.44</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-124.30</t>
+          <t>-122.44</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1487034629.240506</t>
+          <t>1486100140.360955</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>397134872.0</t>
+          <t>297057181.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>519443835.6</v>
+        <v>502139050.6</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>496830876.6</t>
+          <t>492078421.9</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>1422941594.22</v>
+        <v>1372618684.42</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>22612959</t>
+          <t>10060628</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-128661410.195709</t>
+          <t>-124992567.0560451</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-97786961.20784211</t>
+          <t>-104813929.787894</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>397134872.0</t>
+          <t>297057181.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-13.48</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1795,27 +1795,27 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
           <t>30.15</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>30.15</t>
-        </is>
-      </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17565.623</t>
+          <t>13313.072</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1997,17 +1997,17 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,66 +2018,66 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>-0.83</v>
+        <v>-0.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>29.62</v>
+        <v>29.58</v>
       </c>
       <c r="AV4" t="n">
-        <v>31.5</v>
+        <v>31.43</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.51</v>
+        <v>-0.47</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-126.21</t>
+          <t>-124.30</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1487034629.240506</t>
+          <t>1486100140.360955</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>527412360.0</t>
+          <t>397134872.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>540340921.8</v>
+        <v>519443835.6</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>525797781.5</t>
+          <t>496830876.6</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>1500057523.4</v>
+        <v>1422941594.22</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>14543140</t>
+          <t>22612959</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-134274946.3753211</t>
+          <t>-128661410.195709</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-94978652.94320226</t>
+          <t>-97786961.20784211</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>527412360.0</t>
+          <t>397134872.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-13.19</t>
+          <t>-13.48</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2257,27 +2257,27 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22852.342</t>
+          <t>17565.623</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,66 +2480,66 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>75.99</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>-1.46</v>
+        <v>-0.83</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>29.67</v>
+        <v>29.62</v>
       </c>
       <c r="AV5" t="n">
-        <v>31.63</v>
+        <v>31.5</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>33.37</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.55</v>
+        <v>-0.51</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-128.40</t>
+          <t>-126.21</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1487034629.240506</t>
+          <t>1486100140.360955</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>685660828.0</t>
+          <t>527412360.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>580524001.8</v>
+        <v>540340921.8</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>544957176.4</t>
+          <t>525797781.5</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>1690705225.18</v>
+        <v>1500057523.4</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>35566825</t>
+          <t>14543140</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-141419726.9993428</t>
+          <t>-134274946.3753211</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-101532991.5314595</t>
+          <t>-94978652.94320226</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>685660828.0</t>
+          <t>527412360.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>-13.19</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19813.327</t>
+          <t>22852.342</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,66 +2942,66 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>96.83</t>
+          <t>75.99</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>1.23</v>
+        <v>-1.46</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-6.35</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>29.71</v>
+        <v>29.67</v>
       </c>
       <c r="AV6" t="n">
-        <v>31.73</v>
+        <v>31.63</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-130.80</t>
+          <t>-128.40</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1487034629.240506</t>
+          <t>1486100140.360955</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>521844215.6</v>
+        <v>580524001.8</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>543175869.7</t>
+          <t>544957176.4</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>1764344493.16</v>
+        <v>1690705225.18</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-21331654</t>
+          <t>35566825</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-148671860.7207761</t>
+          <t>-141419726.9993428</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-124225347.1028463</t>
+          <t>-101532991.5314595</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3181,27 +3181,27 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12666.27</t>
+          <t>19813.327</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-20.07</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3383,17 +3383,17 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,17 +3404,17 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3423,47 +3423,47 @@
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.66</v>
+        <v>1.57</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.35</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>30.18</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>29.76</v>
+        <v>29.71</v>
       </c>
       <c r="AV7" t="n">
-        <v>31.74</v>
+        <v>31.73</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-0.46</v>
+        <v>-0.38</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.65</v>
+        <v>-0.6</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-133.66</t>
+          <t>-130.80</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1487034629.240506</t>
+          <t>1486100140.360955</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>482017793.2</v>
+        <v>521844215.6</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>603028795.6</t>
+          <t>543175869.7</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>1784609935.56</v>
+        <v>1764344493.16</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-121011002</t>
+          <t>-21331654</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-153116681.3785815</t>
+          <t>-148671860.7207761</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-143395933.8082972</t>
+          <t>-124225347.1028463</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3685,7 +3685,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16538.526</t>
+          <t>12666.27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-29.91</t>
+          <t>-20.07</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,66 +3866,66 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>96.83</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>2.12</v>
+        <v>1.13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.2</v>
+        <v>0.66</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>29.83</v>
+        <v>29.76</v>
       </c>
       <c r="AV8" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-136.11</t>
+          <t>-133.66</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1487034629.240506</t>
+          <t>1486100140.360955</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>474217917.6</v>
+        <v>482017793.2</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>676596050.8</t>
+          <t>603028795.6</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>1797159838.26</v>
+        <v>1784609935.56</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-202378133</t>
+          <t>-121011002</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-154884090.0277241</t>
+          <t>-153116681.3785815</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-142105962.9657878</t>
+          <t>-143395933.8082972</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
@@ -4115,17 +4115,17 @@
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24303.495</t>
+          <t>16538.526</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-30.02</t>
+          <t>-29.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,12 +4328,12 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4343,51 +4343,51 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.09</v>
+        <v>-0.2</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>29.94</v>
+        <v>29.83</v>
       </c>
       <c r="AV9" t="n">
         <v>31.76</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-0.64</v>
+        <v>-0.54</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.74</v>
+        <v>-0.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-138.18</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1487034629.240506</t>
+          <t>1486100140.360955</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>511254641.2</v>
+        <v>474217917.6</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>730553231.8</t>
+          <t>676596050.8</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>1804494052.1</v>
+        <v>1797159838.26</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-219298590</t>
+          <t>-202378133</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-157207385.8571671</t>
+          <t>-154884090.0277241</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-147834991.3348535</t>
+          <t>-142105962.9657878</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4507,22 +4507,22 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4567,27 +4567,27 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13310.128</t>
+          <t>24303.495</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-30.02</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,67 +4790,67 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.84</v>
+        <v>-1.09</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>30.03</v>
+        <v>29.94</v>
       </c>
       <c r="AV10" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="AY10" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>-0.74</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>-0.76</v>
-      </c>
       <c r="BA10" t="inlineStr">
         <is>
           <t>1.94</t>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-139.46</t>
+          <t>-138.18</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1487034629.240506</t>
+          <t>1486100140.360955</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>509390351</v>
+        <v>511254641.2</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>788595268.3</t>
+          <t>730553231.8</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>1812926065.04</v>
+        <v>1804494052.1</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-279204917</t>
+          <t>-219298590</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-158911457.5884969</t>
+          <t>-157207385.8571671</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-175029581.1358453</t>
+          <t>-147834991.3348535</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5029,27 +5029,27 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5081,167 +5081,167 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>13310.128</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-35.41</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-10.74</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/06/12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>28.65</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>27.85</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>0.34</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>13724.475</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-1.42</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-35.30</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-10.89</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/06/12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>27.85</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-2.27</v>
+        <v>-1.84</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>30.18</v>
+        <v>30.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-0.78</v>
+        <v>-0.74</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.77</v>
+        <v>-0.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-139.83</t>
+          <t>-139.46</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1487034629.240506</t>
+          <t>1486100140.360955</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>564507523.8</v>
+        <v>509390351</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>872482288.4</t>
+          <t>788595268.3</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>1847497050.12</v>
+        <v>1812926065.04</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-307974764</t>
+          <t>-279204917</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-155980889.6707972</t>
+          <t>-158911457.5884969</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-171620881.9181248</t>
+          <t>-175029581.1358453</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11713.05</t>
+          <t>13724.475</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-21.86</t>
+          <t>-35.30</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-10.89</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5693,17 +5693,17 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,33 +5714,33 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>175</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>0.03</v>
+        <v>-0.14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-3.38</v>
+        <v>-2.27</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5750,27 +5750,27 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>30.36</v>
+        <v>30.18</v>
       </c>
       <c r="AV12" t="n">
-        <v>31.81</v>
+        <v>31.79</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-0.82</v>
+        <v>-0.78</v>
       </c>
       <c r="AZ12" t="n">
         <v>-0.77</v>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-139.72</t>
+          <t>-139.83</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1487034629.240506</t>
+          <t>1486100140.360955</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>724039798</v>
+        <v>564507523.8</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>926550837.9</t>
+          <t>872482288.4</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>1864715623.88</v>
+        <v>1847497050.12</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-202511039</t>
+          <t>-307974764</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-153137254.7167376</t>
+          <t>-155980889.6707972</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-161911566.145734</t>
+          <t>-171620881.9181248</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>344581728.0</t>
+          <t>404297900.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.64</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>19.44</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>27.17</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>132435</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5953,27 +5953,27 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業平上市</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>-0.05</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>28.65</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>27.85</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>6.70</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>-1.53</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>18566</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>29.58</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>-1.51</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>0.65</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-5.52</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>2.27</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>29.8</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>29.61</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>31.34</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>30.64</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>22.71</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-0.41</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-121.23</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>1486100140.360955</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>547785698.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>491010187.8</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>506427201.7</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>1331487163.14</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>-15417013</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-119348759.9357663</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-88307820.77423298</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>547785698.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>-14.93</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>4.77</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>129350</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>29.8</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>29.35</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>29.35</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>28.65</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>27.85</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>3.58</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>18566</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>52.38</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>46.25</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>0.03</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>1.51</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-5.71</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>30.04</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>29.59</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>31.38</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>30.62</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>33.17</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-0.44</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-122.44</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>1486100140.360955</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>297057181.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>502139050.6</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>492078421.9</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>1372618684.42</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>10060628</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-124992567.0560451</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-104813929.787894</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>297057181.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>-12.90</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>4.77</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>129350</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>30.15</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>29.85</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>30.05</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>28.65</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>27.85</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>4.81</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>18566</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>36.36</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>41.29</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>1.71</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-5.88</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>2.76</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>30.09</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>29.58</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>31.43</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>30.59</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>31.49</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-0.47</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-124.30</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>1486100140.360955</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>397134872.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>519443835.6</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>496830876.6</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>1422941594.22</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>22612959</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-128661410.195709</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-97786961.20784211</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>397134872.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>-13.48</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>4.77</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>129350</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>30.15</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>30.15</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>29.65</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>29.85</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>28.65</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>27.85</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>6.34</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>-1.33</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>18566</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>62.5</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>-0.83</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>1.94</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-5.96</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>3.08</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>30.2</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>29.62</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>31.5</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>30.56</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>33.37</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-0.34</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-0.51</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-126.21</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>1486100140.360955</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>527412360.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>540340921.8</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>525797781.5</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>1500057523.4</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>14543140</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-134274946.3753211</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-94978652.94320226</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>527412360.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>-13.19</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>4.77</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>129350</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>30.25</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>29.8</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>29.95</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>28.65</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>27.85</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>8.25</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-2.68</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>18566</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>37.5</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>75.99</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>-1.46</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>1.92</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-6.2</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>3.57</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>30.24</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>29.67</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>31.63</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>30.54</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>33.88</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-0.55</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-128.40</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>1486100140.360955</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>685660828.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>580524001.8</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>544957176.4</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>1690705225.18</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>35566825</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-141419726.9993428</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-101532991.5314595</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>685660828.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>-13.62</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>4.77</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>129350</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>30.6</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>30.6</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>29.8</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>29.8</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>28.65</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>27.85</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>7.16</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>18566</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>96.83</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>1.23</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-6.35</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>3.95</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>30.18</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>29.71</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>31.73</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>30.52</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>37.05</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-0.38</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-0.6</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-130.80</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>1486100140.360955</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>603430012.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>521844215.6</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>543175869.7</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>1764344493.16</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>-21331654</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-148671860.7207761</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-124225347.1028463</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>603430012.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>-11.45</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>4.77</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>129350</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>30.35</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>30.55</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>30.2</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>30.55</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>28.65</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>27.85</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>4.57</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>-0.33</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>18566</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>90.48</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>96.83</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>1.13</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>0.66</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-6.24</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>4.07</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>29.96</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>29.76</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>31.74</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>29.19</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-0.46</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-0.65</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-133.66</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>1486100140.360955</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>383581106.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>482017793.2</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>603028795.6</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>1784609935.56</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-121011002</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-153116681.3785815</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-143395933.8082972</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>383581106.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>-12.17</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>4.77</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>129350</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>30.55</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>30.15</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>30.3</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>28.65</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>27.85</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>5.97</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>18566</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>96.49</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>2.12</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-6.08</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>4.17</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>29.77</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>29.83</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>31.76</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>22.90</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-0.54</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-136.11</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>1486100140.360955</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>501620303.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>474217917.6</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>676596050.8</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>1797159838.26</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-202378133</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-154884090.0277241</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-142105962.9657878</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>501620303.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>-11.88</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>4.77</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>129350</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>30.2</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>30.4</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>28.65</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>27.85</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>8.78</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>18566</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>91.23</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>1.82</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-1.09</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-5.76</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>4.23</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>29.61</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>29.94</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>31.76</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>30.48</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>13.36</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-0.64</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-0.74</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-138.18</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>1486100140.360955</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>728327760.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>511254641.2</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>730553231.8</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>1804494052.1</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-219298590</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-157207385.8571671</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-147834991.3348535</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>728327760.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>-12.61</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>4.77</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>129350</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>29.7</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>30.25</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>30.15</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>28.65</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>27.85</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>4.81</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>18566</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>89.47</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>82.46</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-1.84</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-5.47</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>4.25</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>29.48</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>30.03</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>31.77</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>30.47</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>3.76</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-0.74</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-0.76</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-139.46</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>1486100140.360955</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>392261897.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>509390351</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>788595268.3</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>1812926065.04</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-279204917</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-158911457.5884969</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-175029581.1358453</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>392261897.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>-14.49</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>4.77</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>129350</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>29.55</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/11/21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>28.65</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/08/25</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>27.85</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>4.96</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-0.51</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>18566</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>84.21</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>85.96</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-2.27</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-5.09</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>4.31</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>29.49</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>30.18</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>31.79</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>30.48</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>-1.06</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-0.78</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-0.77</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>1.94</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-139.83</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/12/02</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>1486100140.360955</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>404297900.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>564507523.8</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>872482288.4</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>1847497050.12</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-307974764</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-155980889.6707972</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-171620881.9181248</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>404297900.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>34.5</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>-14.64</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>仁寶</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>電腦及週邊設備業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-11.1876022432316</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-27.53874609309782</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>-17.9987389236193</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>4.77</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>42.95</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>19.44</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>5.67%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>1.43%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>26.93</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>129350</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>C電子產品99.60%、其他0.40% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>仁寶-電腦及週邊設備業-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>29.55</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>29.75</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>29.45</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>29.17</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 電腦及週邊設備 - 筆記型電腦、工業電腦、伺服器、其他電腦及週邊設備** 平面顯示器 - 電視** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 運動科技 - 穿戴式裝置、健身平台/APP</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18565.916</t>
+          <t>19619.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-10.60</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>29.58</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-1.51</v>
+        <v>-1.08</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>29.61</v>
+        <v>29.64</v>
       </c>
       <c r="AZ2" t="n">
-        <v>31.34</v>
+        <v>31.27</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>30.66</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-121.23</t>
+          <t>-120.41</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1486100140.360955</t>
+          <t>1485229027.321178</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>547785698.0</t>
+          <t>576664362.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>491010187.8</v>
+        <v>469210894.6</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>506427201.7</t>
+          <t>524867448.2</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>1331487163.14</v>
+        <v>1303337000.48</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-15417013</t>
+          <t>-55656553</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-119348759.9357663</t>
+          <t>-112122789.0449276</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-88307820.77423298</t>
+          <t>-72379949.14531446</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>547785698.0</t>
+          <t>576664362.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9910.283</t>
+          <t>18565.916</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>29.58</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.03</v>
+        <v>-1.51</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.51</v>
+        <v>0.65</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>29.59</v>
+        <v>29.61</v>
       </c>
       <c r="AZ3" t="n">
-        <v>31.38</v>
+        <v>31.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-122.44</t>
+          <t>-121.23</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1486100140.360955</t>
+          <t>1485229027.321178</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>297057181.0</t>
+          <t>547785698.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>502139050.6</v>
+        <v>491010187.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>492078421.9</t>
+          <t>506427201.7</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>1372618684.42</v>
+        <v>1331487163.14</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>10060628</t>
+          <t>-15417013</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-124992567.0560451</t>
+          <t>-119348759.9357663</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-104813929.787894</t>
+          <t>-88307820.77423298</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>297057181.0</t>
+          <t>547785698.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13313.072</t>
+          <t>9910.283</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-0.8</v>
+        <v>0.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>29.58</v>
+        <v>29.59</v>
       </c>
       <c r="AZ4" t="n">
-        <v>31.43</v>
+        <v>31.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>33.17</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.32</v>
+        <v>-0.29</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.47</v>
+        <v>-0.44</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-124.30</t>
+          <t>-122.44</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1486100140.360955</t>
+          <t>1485229027.321178</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>397134872.0</t>
+          <t>297057181.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>519443835.6</v>
+        <v>502139050.6</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>496830876.6</t>
+          <t>492078421.9</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>1422941594.22</v>
+        <v>1372618684.42</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>22612959</t>
+          <t>10060628</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-128661410.195709</t>
+          <t>-124992567.0560451</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-97786961.20784211</t>
+          <t>-104813929.787894</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>397134872.0</t>
+          <t>297057181.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-13.48</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
           <t>30.15</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
-        <is>
-          <t>30.15</t>
-        </is>
-      </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17565.623</t>
+          <t>13313.072</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.83</v>
+        <v>-0.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>29.62</v>
+        <v>29.58</v>
       </c>
       <c r="AZ5" t="n">
-        <v>31.5</v>
+        <v>31.43</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.51</v>
+        <v>-0.47</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-126.21</t>
+          <t>-124.30</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1486100140.360955</t>
+          <t>1485229027.321178</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>527412360.0</t>
+          <t>397134872.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>540340921.8</v>
+        <v>519443835.6</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>525797781.5</t>
+          <t>496830876.6</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>1500057523.4</v>
+        <v>1422941594.22</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>14543140</t>
+          <t>22612959</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-134274946.3753211</t>
+          <t>-128661410.195709</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-94978652.94320226</t>
+          <t>-97786961.20784211</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>527412360.0</t>
+          <t>397134872.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-13.19</t>
+          <t>-13.48</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22852.342</t>
+          <t>17565.623</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>75.99</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-1.46</v>
+        <v>-0.83</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>29.67</v>
+        <v>29.62</v>
       </c>
       <c r="AZ6" t="n">
-        <v>31.63</v>
+        <v>31.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>33.37</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.55</v>
+        <v>-0.51</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-128.40</t>
+          <t>-126.21</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1486100140.360955</t>
+          <t>1485229027.321178</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>685660828.0</t>
+          <t>527412360.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>580524001.8</v>
+        <v>540340921.8</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>544957176.4</t>
+          <t>525797781.5</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>1690705225.18</v>
+        <v>1500057523.4</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>35566825</t>
+          <t>14543140</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-141419726.9993428</t>
+          <t>-134274946.3753211</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-101532991.5314595</t>
+          <t>-94978652.94320226</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>685660828.0</t>
+          <t>527412360.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>-13.19</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19813.327</t>
+          <t>22852.342</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>96.83</t>
+          <t>75.99</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1.23</v>
+        <v>-1.46</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-6.35</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>29.71</v>
+        <v>29.67</v>
       </c>
       <c r="AZ7" t="n">
-        <v>31.73</v>
+        <v>31.63</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-130.80</t>
+          <t>-128.40</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1486100140.360955</t>
+          <t>1485229027.321178</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>521844215.6</v>
+        <v>580524001.8</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>543175869.7</t>
+          <t>544957176.4</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>1764344493.16</v>
+        <v>1690705225.18</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-21331654</t>
+          <t>35566825</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-148671860.7207761</t>
+          <t>-141419726.9993428</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-124225347.1028463</t>
+          <t>-101532991.5314595</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12666.27</t>
+          <t>19813.327</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-20.07</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4045,47 +4045,47 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.66</v>
+        <v>1.57</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.35</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>30.18</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>29.76</v>
+        <v>29.71</v>
       </c>
       <c r="AZ8" t="n">
-        <v>31.74</v>
+        <v>31.73</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.46</v>
+        <v>-0.38</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.65</v>
+        <v>-0.6</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-133.66</t>
+          <t>-130.80</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1486100140.360955</t>
+          <t>1485229027.321178</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>482017793.2</v>
+        <v>521844215.6</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>603028795.6</t>
+          <t>543175869.7</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>1784609935.56</v>
+        <v>1764344493.16</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-121011002</t>
+          <t>-21331654</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-153116681.3785815</t>
+          <t>-148671860.7207761</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-143395933.8082972</t>
+          <t>-124225347.1028463</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16538.526</t>
+          <t>12666.27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-29.91</t>
+          <t>-20.07</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>96.83</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>2.12</v>
+        <v>1.13</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.2</v>
+        <v>0.66</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>29.83</v>
+        <v>29.76</v>
       </c>
       <c r="AZ9" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-136.11</t>
+          <t>-133.66</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1486100140.360955</t>
+          <t>1485229027.321178</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>474217917.6</v>
+        <v>482017793.2</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>676596050.8</t>
+          <t>603028795.6</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>1797159838.26</v>
+        <v>1784609935.56</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-202378133</t>
+          <t>-121011002</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-154884090.0277241</t>
+          <t>-153116681.3785815</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-142105962.9657878</t>
+          <t>-143395933.8082972</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4757,17 +4757,17 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24303.495</t>
+          <t>16538.526</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-30.02</t>
+          <t>-29.91</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,12 +4990,12 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5005,51 +5005,51 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AU10" t="n">
-        <v>-1.09</v>
+        <v>-0.2</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>29.94</v>
+        <v>29.83</v>
       </c>
       <c r="AZ10" t="n">
         <v>31.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.64</v>
+        <v>-0.54</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.74</v>
+        <v>-0.7</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-138.18</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1486100140.360955</t>
+          <t>1485229027.321178</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>511254641.2</v>
+        <v>474217917.6</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>730553231.8</t>
+          <t>676596050.8</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>1804494052.1</v>
+        <v>1797159838.26</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-219298590</t>
+          <t>-202378133</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-157207385.8571671</t>
+          <t>-154884090.0277241</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-147834991.3348535</t>
+          <t>-142105962.9657878</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,22 +5169,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13310.128</t>
+          <t>24303.495</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-30.02</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,67 +5472,67 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="AU11" t="n">
-        <v>-1.84</v>
+        <v>-1.09</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>30.03</v>
+        <v>29.94</v>
       </c>
       <c r="AZ11" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="BC11" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="BD11" t="n">
         <v>-0.74</v>
       </c>
-      <c r="BD11" t="n">
-        <v>-0.76</v>
-      </c>
       <c r="BE11" t="inlineStr">
         <is>
           <t>1.94</t>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-139.46</t>
+          <t>-138.18</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1486100140.360955</t>
+          <t>1485229027.321178</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>509390351</v>
+        <v>511254641.2</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>788595268.3</t>
+          <t>730553231.8</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>1812926065.04</v>
+        <v>1804494052.1</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-279204917</t>
+          <t>-219298590</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-158911457.5884969</t>
+          <t>-157207385.8571671</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-175029581.1358453</t>
+          <t>-147834991.3348535</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,22 +5716,22 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5753,7 +5753,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5763,187 +5763,187 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>13310.128</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.53</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-35.41</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>31.4</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>-10.74</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7.36</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025/06/12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>28.65</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2025/08/25</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>27.85</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2025/10/31</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/10/08</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>31.95</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>4.81</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
           <t>0.34</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>13724.475</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-35.30</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>34.3</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>31.4</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-10.89</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7.36</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025/06/12</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>28.65</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2025/08/25</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>27.85</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2025/10/31</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>2025/10/08</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>31.95</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>-0.51</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>19620</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>84.21</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>82.46</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>-2.27</v>
+        <v>-1.84</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.47</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>29.48</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>30.18</v>
+        <v>30.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.47</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-0.78</v>
+        <v>-0.74</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.77</v>
+        <v>-0.76</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-139.83</t>
+          <t>-139.46</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1486100140.360955</t>
+          <t>1485229027.321178</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>564507523.8</v>
+        <v>509390351</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>872482288.4</t>
+          <t>788595268.3</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>1847497050.12</v>
+        <v>1812926065.04</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-307974764</t>
+          <t>-279204917</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-155980889.6707972</t>
+          <t>-158911457.5884969</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-171620881.9181248</t>
+          <t>-175029581.1358453</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>404297900.0</t>
+          <t>392261897.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-14.64</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>19.44</t>
+          <t>19.47</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>129350</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19619.78</t>
+          <t>23491.213</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.60</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-1.08</v>
+        <v>-0.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.25</v>
+        <v>-0.04</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>29.64</v>
+        <v>29.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>31.27</v>
+        <v>31.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>30.66</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BC2" t="n">
         <v>-0.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-120.41</t>
+          <t>-119.70</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1485229027.321178</t>
+          <t>1484611050.926471</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>576664362.0</t>
+          <t>695995921.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>469210894.6</v>
+        <v>502927606.8</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>524867448.2</t>
+          <t>521634264.3</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>1303337000.48</v>
+        <v>1299772662.82</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-55656553</t>
+          <t>-18706657</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-112122789.0449276</t>
+          <t>-102637909.7074677</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-72379949.14531446</t>
+          <t>-50471073.35143852</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>576664362.0</t>
+          <t>695995921.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1373,27 +1373,27 @@
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18565.916</t>
+          <t>19619.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-10.60</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>29.58</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-1.51</v>
+        <v>-1.08</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>29.61</v>
+        <v>29.64</v>
       </c>
       <c r="AZ3" t="n">
-        <v>31.34</v>
+        <v>31.27</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>30.66</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-121.23</t>
+          <t>-120.41</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1485229027.321178</t>
+          <t>1484611050.926471</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>547785698.0</t>
+          <t>576664362.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>491010187.8</v>
+        <v>469210894.6</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>506427201.7</t>
+          <t>524867448.2</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>1331487163.14</v>
+        <v>1303337000.48</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-15417013</t>
+          <t>-55656553</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-119348759.9357663</t>
+          <t>-112122789.0449276</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-88307820.77423298</t>
+          <t>-72379949.14531446</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>547785698.0</t>
+          <t>576664362.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1855,27 +1855,27 @@
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9910.283</t>
+          <t>18565.916</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>29.58</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>0.03</v>
+        <v>-1.51</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.51</v>
+        <v>0.65</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>29.59</v>
+        <v>29.61</v>
       </c>
       <c r="AZ4" t="n">
-        <v>31.38</v>
+        <v>31.34</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-122.44</t>
+          <t>-121.23</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1485229027.321178</t>
+          <t>1484611050.926471</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>297057181.0</t>
+          <t>547785698.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>502139050.6</v>
+        <v>491010187.8</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>492078421.9</t>
+          <t>506427201.7</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>1372618684.42</v>
+        <v>1331487163.14</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>10060628</t>
+          <t>-15417013</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-124992567.0560451</t>
+          <t>-119348759.9357663</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-104813929.787894</t>
+          <t>-88307820.77423298</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>297057181.0</t>
+          <t>547785698.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2337,27 +2337,27 @@
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13313.072</t>
+          <t>9910.283</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-0.8</v>
+        <v>0.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>29.58</v>
+        <v>29.59</v>
       </c>
       <c r="AZ5" t="n">
-        <v>31.43</v>
+        <v>31.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>33.17</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.32</v>
+        <v>-0.29</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.47</v>
+        <v>-0.44</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-124.30</t>
+          <t>-122.44</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1485229027.321178</t>
+          <t>1484611050.926471</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>397134872.0</t>
+          <t>297057181.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>519443835.6</v>
+        <v>502139050.6</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>496830876.6</t>
+          <t>492078421.9</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>1422941594.22</v>
+        <v>1372618684.42</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>22612959</t>
+          <t>10060628</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-128661410.195709</t>
+          <t>-124992567.0560451</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-97786961.20784211</t>
+          <t>-104813929.787894</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>397134872.0</t>
+          <t>297057181.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-13.48</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2819,27 +2819,27 @@
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
           <t>30.15</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
-        <is>
-          <t>30.15</t>
-        </is>
-      </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17565.623</t>
+          <t>13313.072</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.83</v>
+        <v>-0.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>29.62</v>
+        <v>29.58</v>
       </c>
       <c r="AZ6" t="n">
-        <v>31.5</v>
+        <v>31.43</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.51</v>
+        <v>-0.47</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-126.21</t>
+          <t>-124.30</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1485229027.321178</t>
+          <t>1484611050.926471</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>527412360.0</t>
+          <t>397134872.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>540340921.8</v>
+        <v>519443835.6</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>525797781.5</t>
+          <t>496830876.6</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>1500057523.4</v>
+        <v>1422941594.22</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>14543140</t>
+          <t>22612959</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-134274946.3753211</t>
+          <t>-128661410.195709</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-94978652.94320226</t>
+          <t>-97786961.20784211</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>527412360.0</t>
+          <t>397134872.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-13.19</t>
+          <t>-13.48</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3301,27 +3301,27 @@
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22852.342</t>
+          <t>17565.623</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>75.99</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-1.46</v>
+        <v>-0.83</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-5.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>29.67</v>
+        <v>29.62</v>
       </c>
       <c r="AZ7" t="n">
-        <v>31.63</v>
+        <v>31.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>33.37</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.36</v>
+        <v>-0.34</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.55</v>
+        <v>-0.51</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-128.40</t>
+          <t>-126.21</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1485229027.321178</t>
+          <t>1484611050.926471</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>685660828.0</t>
+          <t>527412360.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>580524001.8</v>
+        <v>540340921.8</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>544957176.4</t>
+          <t>525797781.5</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>1690705225.18</v>
+        <v>1500057523.4</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>35566825</t>
+          <t>14543140</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-141419726.9993428</t>
+          <t>-134274946.3753211</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-101532991.5314595</t>
+          <t>-94978652.94320226</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>685660828.0</t>
+          <t>527412360.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-13.62</t>
+          <t>-13.19</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.25</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19813.327</t>
+          <t>22852.342</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-9.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>96.83</t>
+          <t>75.99</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1.23</v>
+        <v>-1.46</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-6.35</t>
+          <t>-6.2</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>29.71</v>
+        <v>29.67</v>
       </c>
       <c r="AZ8" t="n">
-        <v>31.73</v>
+        <v>31.63</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-0.38</v>
+        <v>-0.36</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.6</v>
+        <v>-0.55</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-130.80</t>
+          <t>-128.40</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1485229027.321178</t>
+          <t>1484611050.926471</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>521844215.6</v>
+        <v>580524001.8</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>543175869.7</t>
+          <t>544957176.4</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>1764344493.16</v>
+        <v>1690705225.18</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-21331654</t>
+          <t>35566825</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-148671860.7207761</t>
+          <t>-141419726.9993428</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-124225347.1028463</t>
+          <t>-101532991.5314595</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>603430012.0</t>
+          <t>685660828.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-11.45</t>
+          <t>-13.62</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4265,27 +4265,27 @@
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12666.27</t>
+          <t>19813.327</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-20.07</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-8.32</t>
+          <t>-7.56</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,17 +4508,17 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>90.48</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4527,47 +4527,47 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.66</v>
+        <v>1.57</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.35</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>30.18</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>29.76</v>
+        <v>29.71</v>
       </c>
       <c r="AZ9" t="n">
-        <v>31.74</v>
+        <v>31.73</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-0.46</v>
+        <v>-0.38</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.65</v>
+        <v>-0.6</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-133.66</t>
+          <t>-130.80</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1485229027.321178</t>
+          <t>1484611050.926471</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>482017793.2</v>
+        <v>521844215.6</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>603028795.6</t>
+          <t>543175869.7</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>1784609935.56</v>
+        <v>1764344493.16</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-121011002</t>
+          <t>-21331654</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-153116681.3785815</t>
+          <t>-148671860.7207761</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-143395933.8082972</t>
+          <t>-124225347.1028463</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>383581106.0</t>
+          <t>603430012.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-12.17</t>
+          <t>-11.45</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16538.526</t>
+          <t>12666.27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-29.91</t>
+          <t>-20.07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-8.32</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,66 +4990,66 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.48</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>96.83</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>2.12</v>
+        <v>1.13</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.2</v>
+        <v>0.66</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.24</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>29.96</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>29.83</v>
+        <v>29.76</v>
       </c>
       <c r="AZ10" t="n">
-        <v>31.76</v>
+        <v>31.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.7</v>
+        <v>-0.65</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-136.11</t>
+          <t>-133.66</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1485229027.321178</t>
+          <t>1484611050.926471</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>474217917.6</v>
+        <v>482017793.2</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>676596050.8</t>
+          <t>603028795.6</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>1797159838.26</v>
+        <v>1784609935.56</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-202378133</t>
+          <t>-121011002</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-154884090.0277241</t>
+          <t>-153116681.3785815</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-142105962.9657878</t>
+          <t>-143395933.8082972</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>501620303.0</t>
+          <t>383581106.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>-11.88</t>
+          <t>-12.17</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24303.495</t>
+          <t>16538.526</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-30.02</t>
+          <t>-29.91</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.77</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,12 +5472,12 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5487,51 +5487,51 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>96.49</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="AU11" t="n">
-        <v>-1.09</v>
+        <v>-0.2</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-5.76</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>29.77</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>29.94</v>
+        <v>29.83</v>
       </c>
       <c r="AZ11" t="n">
         <v>31.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-0.64</v>
+        <v>-0.54</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.74</v>
+        <v>-0.7</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-138.18</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1485229027.321178</t>
+          <t>1484611050.926471</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>511254641.2</v>
+        <v>474217917.6</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>730553231.8</t>
+          <t>676596050.8</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>1804494052.1</v>
+        <v>1797159838.26</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-219298590</t>
+          <t>-202378133</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-157207385.8571671</t>
+          <t>-154884090.0277241</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-147834991.3348535</t>
+          <t>-142105962.9657878</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>728327760.0</t>
+          <t>501620303.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-12.61</t>
+          <t>-11.88</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5711,27 +5711,27 @@
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13310.128</t>
+          <t>24303.495</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-35.41</t>
+          <t>-30.02</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-10.74</t>
+          <t>-8.77</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,67 +5954,67 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>82.46</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.82</v>
       </c>
       <c r="AU12" t="n">
-        <v>-1.84</v>
+        <v>-1.09</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-5.76</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>30.03</v>
+        <v>29.94</v>
       </c>
       <c r="AZ12" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>30.47</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>13.36</t>
         </is>
       </c>
       <c r="BC12" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="BD12" t="n">
         <v>-0.74</v>
       </c>
-      <c r="BD12" t="n">
-        <v>-0.76</v>
-      </c>
       <c r="BE12" t="inlineStr">
         <is>
           <t>1.94</t>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-139.46</t>
+          <t>-138.18</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1485229027.321178</t>
+          <t>1484611050.926471</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>509390351</v>
+        <v>511254641.2</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>788595268.3</t>
+          <t>730553231.8</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>1812926065.04</v>
+        <v>1804494052.1</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-279204917</t>
+          <t>-219298590</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-158911457.5884969</t>
+          <t>-157207385.8571671</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-175029581.1358453</t>
+          <t>-147834991.3348535</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>392261897.0</t>
+          <t>728327760.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-12.61</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.57</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>26.64</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>129570</t>
+          <t>130231</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6193,27 +6193,27 @@
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>電腦及週邊設備業右下上市</t>
+          <t>電腦及週邊設備業平上市</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
+          <t>30.25</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/健身平台_APP.xlsx
+++ b/Result/checksun_type/健身平台_APP.xlsx
@@ -948,7 +948,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23491.213</t>
+          <t>21091.968</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-10.14</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>29.17</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
           <t>16.67</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>6.94</t>
-        </is>
-      </c>
       <c r="AT2" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.04</v>
+        <v>-0.19</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>29.64</t>
+          <t>29.61</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>29.65</v>
+        <v>29.67</v>
       </c>
       <c r="AZ2" t="n">
-        <v>31.22</v>
+        <v>31.16</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.71</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>14.36</t>
+          <t>16.20</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-0.33</v>
+        <v>-0.31</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-119.70</t>
+          <t>-118.94</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1484611050.926471</t>
+          <t>1483850777.532168</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>695995921.0</t>
+          <t>627343716.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>502927606.8</v>
+        <v>548969375.6</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>521634264.3</t>
+          <t>534206605.6</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>1299772662.82</v>
+        <v>1288052003.78</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-18706657</t>
+          <t>14762770</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-102637909.7074677</t>
+          <t>-92850846.49661721</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-50471073.35143852</t>
+          <t>-39021998.83693933</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>695995921.0</t>
+          <t>627343716.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-14.35</t>
+          <t>-13.91</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130892</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19619.78</t>
+          <t>23491.213</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.60</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.04</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-1.08</v>
+        <v>-0.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.25</v>
+        <v>-0.04</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-5.03</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>29.64</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>29.64</v>
+        <v>29.65</v>
       </c>
       <c r="AZ3" t="n">
-        <v>31.27</v>
+        <v>31.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>30.66</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BC3" t="n">
         <v>-0.33</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-120.41</t>
+          <t>-119.70</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1484611050.926471</t>
+          <t>1483850777.532168</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>576664362.0</t>
+          <t>695995921.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>469210894.6</v>
+        <v>502927606.8</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>524867448.2</t>
+          <t>521634264.3</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>1303337000.48</v>
+        <v>1299772662.82</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-55656553</t>
+          <t>-18706657</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-112122789.0449276</t>
+          <t>-102637909.7074677</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-72379949.14531446</t>
+          <t>-50471073.35143852</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>576664362.0</t>
+          <t>695995921.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-14.78</t>
+          <t>-14.35</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130892</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18565.916</t>
+          <t>19619.78</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-3.04</t>
+          <t>-10.60</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.20</t>
+          <t>-11.04</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>7.09</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>29.58</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-1.51</v>
+        <v>-1.08</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.72</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>29.61</v>
+        <v>29.64</v>
       </c>
       <c r="AZ4" t="n">
-        <v>31.34</v>
+        <v>31.27</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>30.66</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.41</v>
+        <v>-0.4</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-121.23</t>
+          <t>-120.41</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1484611050.926471</t>
+          <t>1483850777.532168</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>547785698.0</t>
+          <t>576664362.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>491010187.8</v>
+        <v>469210894.6</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>506427201.7</t>
+          <t>524867448.2</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>1331487163.14</v>
+        <v>1303337000.48</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-15417013</t>
+          <t>-55656553</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-119348759.9357663</t>
+          <t>-112122789.0449276</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-88307820.77423298</t>
+          <t>-72379949.14531446</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>547785698.0</t>
+          <t>576664362.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-14.93</t>
+          <t>-14.78</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130892</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9910.283</t>
+          <t>18565.916</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>-3.04</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.08</t>
+          <t>-11.20</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>6.70</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>29.58</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>0.03</v>
+        <v>-1.51</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.51</v>
+        <v>0.65</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>29.59</v>
+        <v>29.61</v>
       </c>
       <c r="AZ5" t="n">
-        <v>31.38</v>
+        <v>31.34</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>33.17</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-122.44</t>
+          <t>-121.23</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1484611050.926471</t>
+          <t>1483850777.532168</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>297057181.0</t>
+          <t>547785698.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>502139050.6</v>
+        <v>491010187.8</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>492078421.9</t>
+          <t>506427201.7</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>1372618684.42</v>
+        <v>1331487163.14</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>10060628</t>
+          <t>-15417013</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-124992567.0560451</t>
+          <t>-119348759.9357663</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-104813929.787894</t>
+          <t>-88307820.77423298</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>297057181.0</t>
+          <t>547785698.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130892</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13313.072</t>
+          <t>9910.283</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.68</t>
+          <t>-9.08</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>46.25</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>-0.8</v>
+        <v>0.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30.09</t>
+          <t>30.04</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>29.58</v>
+        <v>29.59</v>
       </c>
       <c r="AZ6" t="n">
-        <v>31.43</v>
+        <v>31.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>33.17</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-0.32</v>
+        <v>-0.29</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.47</v>
+        <v>-0.44</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-124.30</t>
+          <t>-122.44</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1484611050.926471</t>
+          <t>1483850777.532168</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>397134872.0</t>
+          <t>297057181.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>519443835.6</v>
+        <v>502139050.6</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>496830876.6</t>
+          <t>492078421.9</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>1422941594.22</v>
+        <v>1372618684.42</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>22612959</t>
+          <t>10060628</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-128661410.195709</t>
+          <t>-124992567.0560451</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-97786961.20784211</t>
+          <t>-104813929.787894</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>397134872.0</t>
+          <t>297057181.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-13.48</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130892</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
+          <t>30.0</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
           <t>30.15</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>30.15</t>
-        </is>
-      </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17565.623</t>
+          <t>13313.072</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.38</t>
+          <t>-9.68</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>41.29</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>-0.83</v>
+        <v>-0.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-5.96</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>30.09</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>29.62</v>
+        <v>29.58</v>
       </c>
       <c r="AZ7" t="n">
-        <v>31.5</v>
+        <v>31.43</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>31.49</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.51</v>
+        <v>-0.47</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-126.21</t>
+          <t>-124.30</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1484611050.926471</t>
+          <t>1483850777.532168</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>527412360.0</t>
+          <t>397134872.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>540340921.8</v>
+        <v>519443835.6</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>525797781.5</t>
+          <t>496830876.6</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>1500057523.4</v>
+        <v>1422941594.22</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>14543140</t>
+          <t>22612959</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-134274946.3753211</t>
+          <t>-128661410.195709</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-94978652.94320226</t>
+          <t>-97786961.20784211</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>527412360.0</t>
+          <t>397134872.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-13.19</t>
+          <t>-13.48</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>19.67</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>26.35</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>130231</t>
+          <t>130892</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.65</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>29.95</t>
+          <t>29.85</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>22852.342</t>
+          <t>17565.623</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.83</t>
+          <t>-9.38</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
 